--- a/voti_contro.xlsx
+++ b/voti_contro.xlsx
@@ -49,64 +49,64 @@
     <t>MediaConMod_D</t>
   </si>
   <si>
+    <t>EMPOLI</t>
+  </si>
+  <si>
+    <t>JUVENTUS</t>
+  </si>
+  <si>
+    <t>VERONA</t>
+  </si>
+  <si>
+    <t>GENOA</t>
+  </si>
+  <si>
+    <t>TORINO</t>
+  </si>
+  <si>
+    <t>FIORENTINA</t>
+  </si>
+  <si>
+    <t>LECCE</t>
+  </si>
+  <si>
+    <t>ROMA</t>
+  </si>
+  <si>
+    <t>BOLOGNA</t>
+  </si>
+  <si>
     <t>CAGLIARI</t>
   </si>
   <si>
-    <t>ROMA</t>
-  </si>
-  <si>
-    <t>BOLOGNA</t>
-  </si>
-  <si>
-    <t>VERONA</t>
-  </si>
-  <si>
-    <t>GENOA</t>
+    <t>UDINESE</t>
+  </si>
+  <si>
+    <t>ATALANTA</t>
+  </si>
+  <si>
+    <t>NAPOLI</t>
+  </si>
+  <si>
+    <t>INTER</t>
+  </si>
+  <si>
+    <t>MONZA</t>
+  </si>
+  <si>
+    <t>SALERNITANA</t>
+  </si>
+  <si>
+    <t>MILAN</t>
+  </si>
+  <si>
+    <t>SASSUOLO</t>
+  </si>
+  <si>
+    <t>LAZIO</t>
   </si>
   <si>
     <t>FROSINONE</t>
-  </si>
-  <si>
-    <t>LAZIO</t>
-  </si>
-  <si>
-    <t>SALERNITANA</t>
-  </si>
-  <si>
-    <t>INTER</t>
-  </si>
-  <si>
-    <t>MONZA</t>
-  </si>
-  <si>
-    <t>ATALANTA</t>
-  </si>
-  <si>
-    <t>NAPOLI</t>
-  </si>
-  <si>
-    <t>UDINESE</t>
-  </si>
-  <si>
-    <t>JUVENTUS</t>
-  </si>
-  <si>
-    <t>EMPOLI</t>
-  </si>
-  <si>
-    <t>LECCE</t>
-  </si>
-  <si>
-    <t>TORINO</t>
-  </si>
-  <si>
-    <t>FIORENTINA</t>
-  </si>
-  <si>
-    <t>MILAN</t>
-  </si>
-  <si>
-    <t>SASSUOLO</t>
   </si>
 </sst>
 </file>
@@ -513,31 +513,31 @@
         <v>6.125</v>
       </c>
       <c r="D2">
-        <v>5.822222222222222</v>
+        <v>6.184782608695652</v>
       </c>
       <c r="E2">
-        <v>6.081395348837209</v>
+        <v>6.075757575757576</v>
       </c>
       <c r="F2">
-        <v>6.204545454545454</v>
+        <v>6.0625</v>
       </c>
       <c r="G2">
-        <v>4.5625</v>
+        <v>5.5</v>
       </c>
       <c r="H2">
-        <v>5.822222222222222</v>
+        <v>6.326086956521739</v>
       </c>
       <c r="I2">
-        <v>6.558139534883721</v>
+        <v>6.348484848484849</v>
       </c>
       <c r="J2">
-        <v>6.886363636363637</v>
+        <v>6.708333333333333</v>
       </c>
       <c r="K2">
-        <v>4.9375</v>
+        <v>5.9375</v>
       </c>
       <c r="L2">
-        <v>6.1</v>
+        <v>6.831521739130435</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -548,34 +548,34 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="D3">
-        <v>5.894736842105263</v>
+        <v>6.1</v>
       </c>
       <c r="E3">
-        <v>6.078947368421052</v>
+        <v>6.054347826086956</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>5.958333333333333</v>
       </c>
       <c r="G3">
-        <v>4.375</v>
+        <v>5.4375</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.457142857142857</v>
       </c>
       <c r="I3">
-        <v>6.355263157894737</v>
+        <v>6.076086956521739</v>
       </c>
       <c r="J3">
-        <v>6.318181818181818</v>
+        <v>6.125</v>
       </c>
       <c r="K3">
-        <v>4.65625</v>
+        <v>6.3125</v>
       </c>
       <c r="L3">
-        <v>6.289473684210527</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -586,34 +586,34 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>6.1875</v>
+        <v>5.8125</v>
       </c>
       <c r="D4">
-        <v>5.936170212765957</v>
+        <v>5.790697674418604</v>
       </c>
       <c r="E4">
-        <v>5.761904761904762</v>
+        <v>6.034090909090909</v>
       </c>
       <c r="F4">
-        <v>5.894736842105263</v>
+        <v>5.921052631578948</v>
       </c>
       <c r="G4">
-        <v>4.875</v>
+        <v>4.5625</v>
       </c>
       <c r="H4">
-        <v>5.893617021276595</v>
+        <v>5.802325581395348</v>
       </c>
       <c r="I4">
-        <v>5.702380952380953</v>
+        <v>6.386363636363637</v>
       </c>
       <c r="J4">
-        <v>6.157894736842105</v>
+        <v>6.631578947368421</v>
       </c>
       <c r="K4">
-        <v>5.5</v>
+        <v>4.9375</v>
       </c>
       <c r="L4">
-        <v>6.175531914893617</v>
+        <v>6.081395348837209</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -624,34 +624,34 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>5.9375</v>
+        <v>6.1875</v>
       </c>
       <c r="D5">
-        <v>5.95</v>
+        <v>5.73170731707317</v>
       </c>
       <c r="E5">
-        <v>6.134146341463414</v>
+        <v>5.964285714285714</v>
       </c>
       <c r="F5">
-        <v>5.761904761904762</v>
+        <v>5.928571428571429</v>
       </c>
       <c r="G5">
-        <v>4.9375</v>
+        <v>4.6875</v>
       </c>
       <c r="H5">
-        <v>5.9625</v>
+        <v>5.75609756097561</v>
       </c>
       <c r="I5">
-        <v>6.524390243902439</v>
+        <v>6.238095238095238</v>
       </c>
       <c r="J5">
-        <v>6.047619047619047</v>
+        <v>6.452380952380953</v>
       </c>
       <c r="K5">
-        <v>5.25</v>
+        <v>5.125</v>
       </c>
       <c r="L5">
-        <v>6.29375</v>
+        <v>6.048780487804878</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -662,34 +662,34 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>6.3125</v>
+        <v>6.1875</v>
       </c>
       <c r="D6">
-        <v>5.806818181818182</v>
+        <v>5.878048780487805</v>
       </c>
       <c r="E6">
-        <v>6.119047619047619</v>
+        <v>5.963414634146342</v>
       </c>
       <c r="F6">
-        <v>5.875</v>
+        <v>6.041666666666667</v>
       </c>
       <c r="G6">
-        <v>5.4375</v>
+        <v>5.1875</v>
       </c>
       <c r="H6">
-        <v>5.738636363636363</v>
+        <v>5.804878048780488</v>
       </c>
       <c r="I6">
-        <v>6.630952380952381</v>
+        <v>6.195121951219512</v>
       </c>
       <c r="J6">
-        <v>6.1875</v>
+        <v>6.5</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>5.6875</v>
       </c>
       <c r="L6">
-        <v>5.988636363636363</v>
+        <v>6.140243902439025</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -700,34 +700,34 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>6.125</v>
+        <v>6.3125</v>
       </c>
       <c r="D7">
-        <v>5.7625</v>
+        <v>5.837209302325581</v>
       </c>
       <c r="E7">
-        <v>5.977777777777778</v>
+        <v>5.953488372093023</v>
       </c>
       <c r="F7">
-        <v>5.975</v>
+        <v>6.113636363636363</v>
       </c>
       <c r="G7">
-        <v>5.375</v>
+        <v>4.5625</v>
       </c>
       <c r="H7">
-        <v>5.6375</v>
+        <v>5.918604651162791</v>
       </c>
       <c r="I7">
-        <v>6.255555555555556</v>
+        <v>6.197674418604652</v>
       </c>
       <c r="J7">
-        <v>6.175</v>
+        <v>6.704545454545454</v>
       </c>
       <c r="K7">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="L7">
-        <v>5.86875</v>
+        <v>6.215116279069767</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -741,31 +741,31 @@
         <v>6.375</v>
       </c>
       <c r="D8">
-        <v>5.878048780487805</v>
+        <v>5.888888888888889</v>
       </c>
       <c r="E8">
-        <v>5.829268292682927</v>
+        <v>5.920454545454546</v>
       </c>
       <c r="F8">
-        <v>6.025</v>
+        <v>5.954545454545454</v>
       </c>
       <c r="G8">
-        <v>4.9375</v>
+        <v>5.5625</v>
       </c>
       <c r="H8">
-        <v>5.890243902439025</v>
+        <v>5.9</v>
       </c>
       <c r="I8">
-        <v>5.878048780487805</v>
+        <v>6.193181818181818</v>
       </c>
       <c r="J8">
-        <v>6.475</v>
+        <v>6.477272727272728</v>
       </c>
       <c r="K8">
-        <v>5.65625</v>
+        <v>6.21875</v>
       </c>
       <c r="L8">
-        <v>6.170731707317073</v>
+        <v>6.233333333333333</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -776,34 +776,34 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>6.166666666666667</v>
+        <v>6.1875</v>
       </c>
       <c r="D9">
-        <v>6.127906976744186</v>
+        <v>5.9875</v>
       </c>
       <c r="E9">
-        <v>6.22093023255814</v>
+        <v>6.135135135135135</v>
       </c>
       <c r="F9">
-        <v>6.444444444444445</v>
+        <v>6.104166666666667</v>
       </c>
       <c r="G9">
+        <v>5.0625</v>
+      </c>
+      <c r="H9">
+        <v>6.1125</v>
+      </c>
+      <c r="I9">
+        <v>6.486486486486487</v>
+      </c>
+      <c r="J9">
+        <v>6.395833333333333</v>
+      </c>
+      <c r="K9">
         <v>5.5</v>
       </c>
-      <c r="H9">
-        <v>6.325581395348837</v>
-      </c>
-      <c r="I9">
-        <v>6.906976744186046</v>
-      </c>
-      <c r="J9">
-        <v>7.666666666666667</v>
-      </c>
-      <c r="K9">
-        <v>6.027777777777778</v>
-      </c>
       <c r="L9">
-        <v>6.767441860465116</v>
+        <v>6.4875</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -814,34 +814,34 @@
         <v>19</v>
       </c>
       <c r="C10">
-        <v>6.125</v>
+        <v>6.0625</v>
       </c>
       <c r="D10">
-        <v>5.723404255319149</v>
+        <v>5.738095238095238</v>
       </c>
       <c r="E10">
-        <v>5.686046511627907</v>
+        <v>5.707317073170731</v>
       </c>
       <c r="F10">
-        <v>5.970588235294118</v>
+        <v>5.975</v>
       </c>
       <c r="G10">
-        <v>4.375</v>
+        <v>4.5</v>
       </c>
       <c r="H10">
-        <v>5.723404255319149</v>
+        <v>5.571428571428571</v>
       </c>
       <c r="I10">
-        <v>5.732558139534884</v>
+        <v>5.573170731707317</v>
       </c>
       <c r="J10">
-        <v>6.088235294117647</v>
+        <v>6.5</v>
       </c>
       <c r="K10">
-        <v>4.78125</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>5.941489361702128</v>
+        <v>5.779761904761905</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -852,34 +852,34 @@
         <v>20</v>
       </c>
       <c r="C11">
-        <v>6.0625</v>
+        <v>6.125</v>
       </c>
       <c r="D11">
-        <v>5.964285714285714</v>
+        <v>5.840425531914893</v>
       </c>
       <c r="E11">
-        <v>6.085365853658536</v>
+        <v>6.089743589743589</v>
       </c>
       <c r="F11">
-        <v>6.261904761904762</v>
+        <v>6.28</v>
       </c>
       <c r="G11">
-        <v>4.875</v>
+        <v>4.6875</v>
       </c>
       <c r="H11">
-        <v>5.892857142857143</v>
+        <v>5.840425531914893</v>
       </c>
       <c r="I11">
-        <v>6.402439024390244</v>
+        <v>6.653846153846154</v>
       </c>
       <c r="J11">
-        <v>7.595238095238095</v>
+        <v>7.18</v>
       </c>
       <c r="K11">
-        <v>5.1875</v>
+        <v>5.0625</v>
       </c>
       <c r="L11">
-        <v>6.238095238095238</v>
+        <v>6.101063829787234</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -890,34 +890,34 @@
         <v>21</v>
       </c>
       <c r="C12">
-        <v>6.1875</v>
+        <v>6.0625</v>
       </c>
       <c r="D12">
-        <v>5.925</v>
+        <v>5.895348837209302</v>
       </c>
       <c r="E12">
-        <v>5.96875</v>
+        <v>6.071428571428571</v>
       </c>
       <c r="F12">
-        <v>6.136363636363637</v>
+        <v>6.181818181818182</v>
       </c>
       <c r="G12">
-        <v>4.5625</v>
+        <v>5.0625</v>
       </c>
       <c r="H12">
-        <v>6.1875</v>
+        <v>5.86046511627907</v>
       </c>
       <c r="I12">
-        <v>6.260416666666667</v>
+        <v>6.369047619047619</v>
       </c>
       <c r="J12">
-        <v>6.681818181818182</v>
+        <v>6.727272727272728</v>
       </c>
       <c r="K12">
-        <v>5.03125</v>
+        <v>5.40625</v>
       </c>
       <c r="L12">
-        <v>6.5875</v>
+        <v>6.133720930232558</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -928,34 +928,34 @@
         <v>22</v>
       </c>
       <c r="C13">
-        <v>6.4375</v>
+        <v>6.1875</v>
       </c>
       <c r="D13">
-        <v>5.857142857142857</v>
+        <v>5.634146341463414</v>
       </c>
       <c r="E13">
-        <v>5.951219512195122</v>
+        <v>5.797872340425532</v>
       </c>
       <c r="F13">
-        <v>6.340909090909091</v>
+        <v>5.863636363636363</v>
       </c>
       <c r="G13">
+        <v>4.1875</v>
+      </c>
+      <c r="H13">
+        <v>5.658536585365853</v>
+      </c>
+      <c r="I13">
+        <v>6.074468085106383</v>
+      </c>
+      <c r="J13">
+        <v>6.090909090909091</v>
+      </c>
+      <c r="K13">
         <v>4.6875</v>
       </c>
-      <c r="H13">
-        <v>5.833333333333333</v>
-      </c>
-      <c r="I13">
-        <v>6.329268292682927</v>
-      </c>
-      <c r="J13">
-        <v>7.386363636363637</v>
-      </c>
-      <c r="K13">
-        <v>5.5625</v>
-      </c>
       <c r="L13">
-        <v>6.279761904761905</v>
+        <v>5.853658536585366</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -966,34 +966,34 @@
         <v>23</v>
       </c>
       <c r="C14">
-        <v>6.1875</v>
+        <v>6.5</v>
       </c>
       <c r="D14">
-        <v>5.918604651162791</v>
+        <v>6.130952380952381</v>
       </c>
       <c r="E14">
-        <v>6.182926829268292</v>
+        <v>6.158536585365853</v>
       </c>
       <c r="F14">
-        <v>6.086956521739131</v>
+        <v>6.384615384615385</v>
       </c>
       <c r="G14">
-        <v>5.3125</v>
+        <v>5.5</v>
       </c>
       <c r="H14">
-        <v>5.906976744186046</v>
+        <v>6.321428571428571</v>
       </c>
       <c r="I14">
-        <v>6.646341463414634</v>
+        <v>6.512195121951219</v>
       </c>
       <c r="J14">
-        <v>6.521739130434782</v>
+        <v>7.346153846153846</v>
       </c>
       <c r="K14">
-        <v>5.8125</v>
+        <v>6.46875</v>
       </c>
       <c r="L14">
-        <v>6.197674418604652</v>
+        <v>6.898809523809524</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1007,31 +1007,31 @@
         <v>6.1875</v>
       </c>
       <c r="D15">
-        <v>6.027027027027027</v>
+        <v>5.782608695652174</v>
       </c>
       <c r="E15">
-        <v>6.059523809523809</v>
+        <v>5.837209302325581</v>
       </c>
       <c r="F15">
-        <v>5.958333333333333</v>
+        <v>6.058823529411764</v>
       </c>
       <c r="G15">
-        <v>5.4375</v>
+        <v>4.1875</v>
       </c>
       <c r="H15">
-        <v>6.135135135135135</v>
+        <v>5.771739130434782</v>
       </c>
       <c r="I15">
-        <v>6.261904761904762</v>
+        <v>6.011627906976744</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>6.441176470588236</v>
       </c>
       <c r="K15">
-        <v>5.875</v>
+        <v>4.71875</v>
       </c>
       <c r="L15">
-        <v>6.52027027027027</v>
+        <v>6.076086956521739</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1042,34 +1042,34 @@
         <v>25</v>
       </c>
       <c r="C16">
-        <v>6.0625</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>6.166666666666667</v>
+        <v>5.95</v>
       </c>
       <c r="E16">
         <v>6.141025641025641</v>
       </c>
       <c r="F16">
-        <v>6.090909090909091</v>
+        <v>6.282608695652174</v>
       </c>
       <c r="G16">
-        <v>5.5</v>
+        <v>5.125</v>
       </c>
       <c r="H16">
-        <v>6.288888888888889</v>
+        <v>5.8625</v>
       </c>
       <c r="I16">
-        <v>6.410256410256411</v>
+        <v>6.487179487179487</v>
       </c>
       <c r="J16">
-        <v>6.795454545454546</v>
+        <v>7.391304347826087</v>
       </c>
       <c r="K16">
-        <v>5.84375</v>
+        <v>5.375</v>
       </c>
       <c r="L16">
-        <v>6.777777777777778</v>
+        <v>6.1625</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1080,34 +1080,34 @@
         <v>26</v>
       </c>
       <c r="C17">
-        <v>6.3125</v>
+        <v>6.055555555555555</v>
       </c>
       <c r="D17">
-        <v>5.736842105263158</v>
+        <v>6.131578947368421</v>
       </c>
       <c r="E17">
-        <v>5.901960784313726</v>
+        <v>6.25531914893617</v>
       </c>
       <c r="F17">
-        <v>5.809523809523809</v>
+        <v>6.222222222222222</v>
       </c>
       <c r="G17">
-        <v>5.1875</v>
+        <v>5.388888888888889</v>
       </c>
       <c r="H17">
-        <v>5.631578947368421</v>
+        <v>6.315789473684211</v>
       </c>
       <c r="I17">
-        <v>6.068627450980392</v>
+        <v>7.117021276595745</v>
       </c>
       <c r="J17">
-        <v>6.190476190476191</v>
+        <v>7.111111111111111</v>
       </c>
       <c r="K17">
-        <v>5.78125</v>
+        <v>5.694444444444445</v>
       </c>
       <c r="L17">
-        <v>5.881578947368421</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1118,34 +1118,34 @@
         <v>27</v>
       </c>
       <c r="C18">
-        <v>6.375</v>
+        <v>6.3125</v>
       </c>
       <c r="D18">
-        <v>5.953488372093023</v>
+        <v>5.895348837209302</v>
       </c>
       <c r="E18">
-        <v>5.841463414634147</v>
+        <v>6.088235294117647</v>
       </c>
       <c r="F18">
-        <v>6.04</v>
+        <v>6.134615384615385</v>
       </c>
       <c r="G18">
-        <v>5.625</v>
+        <v>4.0625</v>
       </c>
       <c r="H18">
-        <v>5.883720930232558</v>
+        <v>6.058139534883721</v>
       </c>
       <c r="I18">
-        <v>5.975609756097561</v>
+        <v>6.338235294117647</v>
       </c>
       <c r="J18">
-        <v>6.46</v>
+        <v>6.980769230769231</v>
       </c>
       <c r="K18">
-        <v>6.3125</v>
+        <v>4.6875</v>
       </c>
       <c r="L18">
-        <v>6.174418604651163</v>
+        <v>6.453488372093023</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1156,34 +1156,34 @@
         <v>28</v>
       </c>
       <c r="C19">
-        <v>6.4375</v>
+        <v>5.9375</v>
       </c>
       <c r="D19">
-        <v>5.813953488372093</v>
+        <v>6.097560975609756</v>
       </c>
       <c r="E19">
-        <v>5.877777777777778</v>
+        <v>6.174418604651163</v>
       </c>
       <c r="F19">
-        <v>5.833333333333333</v>
+        <v>6.227272727272728</v>
       </c>
       <c r="G19">
-        <v>5.1875</v>
+        <v>4.8125</v>
       </c>
       <c r="H19">
-        <v>5.918604651162791</v>
+        <v>6.292682926829269</v>
       </c>
       <c r="I19">
-        <v>6.144444444444445</v>
+        <v>6.709302325581396</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>7.340909090909091</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>5.03125</v>
       </c>
       <c r="L19">
-        <v>6.203488372093023</v>
+        <v>6.829268292682927</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1194,34 +1194,34 @@
         <v>29</v>
       </c>
       <c r="C20">
-        <v>6.4375</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>5.77906976744186</v>
+        <v>5.920454545454546</v>
       </c>
       <c r="E20">
-        <v>5.947368421052632</v>
+        <v>5.75</v>
       </c>
       <c r="F20">
-        <v>6.018518518518518</v>
+        <v>5.909090909090909</v>
       </c>
       <c r="G20">
-        <v>4.6875</v>
+        <v>4.5</v>
       </c>
       <c r="H20">
-        <v>5.72093023255814</v>
+        <v>5.988636363636363</v>
       </c>
       <c r="I20">
-        <v>5.960526315789473</v>
+        <v>5.785714285714286</v>
       </c>
       <c r="J20">
-        <v>6.537037037037037</v>
+        <v>6.227272727272728</v>
       </c>
       <c r="K20">
-        <v>5.40625</v>
+        <v>4.84375</v>
       </c>
       <c r="L20">
-        <v>5.994186046511628</v>
+        <v>6.289772727272728</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1232,34 +1232,34 @@
         <v>30</v>
       </c>
       <c r="C21">
-        <v>6.0625</v>
+        <v>6.3125</v>
       </c>
       <c r="D21">
-        <v>6.065789473684211</v>
+        <v>5.825581395348837</v>
       </c>
       <c r="E21">
-        <v>6.166666666666667</v>
+        <v>5.956521739130435</v>
       </c>
       <c r="F21">
-        <v>6.166666666666667</v>
+        <v>5.95</v>
       </c>
       <c r="G21">
-        <v>5.0625</v>
+        <v>5.8125</v>
       </c>
       <c r="H21">
-        <v>6.236842105263158</v>
+        <v>5.744186046511628</v>
       </c>
       <c r="I21">
-        <v>6.619047619047619</v>
+        <v>6.163043478260869</v>
       </c>
       <c r="J21">
-        <v>7.083333333333333</v>
+        <v>6.575</v>
       </c>
       <c r="K21">
-        <v>5.40625</v>
+        <v>6.40625</v>
       </c>
       <c r="L21">
-        <v>6.736842105263158</v>
+        <v>6.034883720930233</v>
       </c>
     </row>
   </sheetData>

--- a/voti_contro.xlsx
+++ b/voti_contro.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>squadra</t>
   </si>
@@ -49,64 +49,73 @@
     <t>MediaConMod_D</t>
   </si>
   <si>
+    <t>BOLOGNA</t>
+  </si>
+  <si>
+    <t>CAGLIARI</t>
+  </si>
+  <si>
+    <t>ROMA</t>
+  </si>
+  <si>
+    <t>COMO</t>
+  </si>
+  <si>
+    <t>LECCE</t>
+  </si>
+  <si>
+    <t>TORINO</t>
+  </si>
+  <si>
+    <t>FIORENTINA</t>
+  </si>
+  <si>
+    <t>VENEZIA</t>
+  </si>
+  <si>
+    <t>LAZIO</t>
+  </si>
+  <si>
+    <t>FROSINONE</t>
+  </si>
+  <si>
+    <t>INTER</t>
+  </si>
+  <si>
+    <t>MONZA</t>
+  </si>
+  <si>
+    <t>SALERNITANA</t>
+  </si>
+  <si>
     <t>GENOA</t>
   </si>
   <si>
     <t>VERONA</t>
   </si>
   <si>
+    <t>MILAN</t>
+  </si>
+  <si>
+    <t>PARMA</t>
+  </si>
+  <si>
+    <t>SASSUOLO</t>
+  </si>
+  <si>
+    <t>ATALANTA</t>
+  </si>
+  <si>
+    <t>NAPOLI</t>
+  </si>
+  <si>
+    <t>UDINESE</t>
+  </si>
+  <si>
     <t>EMPOLI</t>
   </si>
   <si>
     <t>JUVENTUS</t>
-  </si>
-  <si>
-    <t>LAZIO</t>
-  </si>
-  <si>
-    <t>FROSINONE</t>
-  </si>
-  <si>
-    <t>BOLOGNA</t>
-  </si>
-  <si>
-    <t>CAGLIARI</t>
-  </si>
-  <si>
-    <t>ROMA</t>
-  </si>
-  <si>
-    <t>INTER</t>
-  </si>
-  <si>
-    <t>MONZA</t>
-  </si>
-  <si>
-    <t>SALERNITANA</t>
-  </si>
-  <si>
-    <t>NAPOLI</t>
-  </si>
-  <si>
-    <t>UDINESE</t>
-  </si>
-  <si>
-    <t>ATALANTA</t>
-  </si>
-  <si>
-    <t>LECCE</t>
-  </si>
-  <si>
-    <t>TORINO</t>
-  </si>
-  <si>
-    <t>FIORENTINA</t>
-  </si>
-  <si>
-    <t>MILAN</t>
-  </si>
-  <si>
-    <t>SASSUOLO</t>
   </si>
 </sst>
 </file>
@@ -464,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -510,34 +519,34 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>6.3125</v>
+        <v>6.125</v>
       </c>
       <c r="D2">
-        <v>5.806818181818182</v>
+        <v>5.880952380952381</v>
       </c>
       <c r="E2">
-        <v>6.119047619047619</v>
+        <v>5.82051282051282</v>
       </c>
       <c r="F2">
-        <v>5.875</v>
+        <v>5.976190476190476</v>
       </c>
       <c r="G2">
-        <v>5.4375</v>
+        <v>4.6875</v>
       </c>
       <c r="H2">
-        <v>5.738636363636363</v>
+        <v>5.809523809523809</v>
       </c>
       <c r="I2">
-        <v>6.630952380952381</v>
+        <v>5.807692307692307</v>
       </c>
       <c r="J2">
-        <v>6.1875</v>
+        <v>6.5</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>5.21875</v>
       </c>
       <c r="L2">
-        <v>5.988636363636363</v>
+        <v>6.142857142857143</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -548,34 +557,34 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>5.9375</v>
+        <v>6.1875</v>
       </c>
       <c r="D3">
-        <v>5.95</v>
+        <v>5.891304347826087</v>
       </c>
       <c r="E3">
-        <v>6.134146341463414</v>
+        <v>6.192307692307693</v>
       </c>
       <c r="F3">
-        <v>5.761904761904762</v>
+        <v>6.185185185185185</v>
       </c>
       <c r="G3">
-        <v>4.9375</v>
+        <v>4.875</v>
       </c>
       <c r="H3">
-        <v>5.9625</v>
+        <v>5.934782608695652</v>
       </c>
       <c r="I3">
-        <v>6.524390243902439</v>
+        <v>6.935897435897436</v>
       </c>
       <c r="J3">
-        <v>6.047619047619047</v>
+        <v>6.814814814814815</v>
       </c>
       <c r="K3">
-        <v>5.25</v>
+        <v>5.3125</v>
       </c>
       <c r="L3">
-        <v>6.29375</v>
+        <v>6.211956521739131</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -586,34 +595,34 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>6.0625</v>
+        <v>6.1875</v>
       </c>
       <c r="D4">
-        <v>6.166666666666667</v>
+        <v>6.048780487804878</v>
       </c>
       <c r="E4">
-        <v>6.141025641025641</v>
+        <v>6.175675675675675</v>
       </c>
       <c r="F4">
-        <v>6.090909090909091</v>
+        <v>6.282608695652174</v>
       </c>
       <c r="G4">
+        <v>5.0625</v>
+      </c>
+      <c r="H4">
+        <v>6.170731707317073</v>
+      </c>
+      <c r="I4">
+        <v>6.54054054054054</v>
+      </c>
+      <c r="J4">
+        <v>6.913043478260869</v>
+      </c>
+      <c r="K4">
         <v>5.5</v>
       </c>
-      <c r="H4">
-        <v>6.288888888888889</v>
-      </c>
-      <c r="I4">
-        <v>6.410256410256411</v>
-      </c>
-      <c r="J4">
-        <v>6.795454545454546</v>
-      </c>
-      <c r="K4">
-        <v>5.84375</v>
-      </c>
       <c r="L4">
-        <v>6.777777777777778</v>
+        <v>6.573170731707317</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -624,34 +633,34 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>6.1875</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>6.027027027027027</v>
+        <v>6.3</v>
       </c>
       <c r="E5">
-        <v>6.059523809523809</v>
+        <v>6.4</v>
       </c>
       <c r="F5">
-        <v>5.958333333333333</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="G5">
-        <v>5.4375</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>6.135135135135135</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>6.261904761904762</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K5">
-        <v>5.875</v>
+        <v>6.25</v>
       </c>
       <c r="L5">
-        <v>6.52027027027027</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -662,34 +671,34 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>6.375</v>
+        <v>6.25</v>
       </c>
       <c r="D6">
-        <v>5.878048780487805</v>
+        <v>5.944444444444445</v>
       </c>
       <c r="E6">
-        <v>5.829268292682927</v>
+        <v>5.95</v>
       </c>
       <c r="F6">
-        <v>6.025</v>
+        <v>5.98</v>
       </c>
       <c r="G6">
-        <v>4.9375</v>
+        <v>5.4375</v>
       </c>
       <c r="H6">
-        <v>5.890243902439025</v>
+        <v>5.988888888888889</v>
       </c>
       <c r="I6">
-        <v>5.878048780487805</v>
+        <v>6.275</v>
       </c>
       <c r="J6">
-        <v>6.475</v>
+        <v>6.44</v>
       </c>
       <c r="K6">
-        <v>5.65625</v>
+        <v>5.96875</v>
       </c>
       <c r="L6">
-        <v>6.170731707317073</v>
+        <v>6.372222222222222</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -700,34 +709,34 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>6.125</v>
+        <v>6.222222222222222</v>
       </c>
       <c r="D7">
-        <v>5.7625</v>
+        <v>5.85</v>
       </c>
       <c r="E7">
-        <v>5.977777777777778</v>
+        <v>6.024390243902439</v>
       </c>
       <c r="F7">
-        <v>5.975</v>
+        <v>6.04</v>
       </c>
       <c r="G7">
-        <v>5.375</v>
+        <v>5.444444444444445</v>
       </c>
       <c r="H7">
-        <v>5.6375</v>
+        <v>5.7125</v>
       </c>
       <c r="I7">
-        <v>6.255555555555556</v>
+        <v>6.378048780487805</v>
       </c>
       <c r="J7">
-        <v>6.175</v>
+        <v>6.58</v>
       </c>
       <c r="K7">
-        <v>5.75</v>
+        <v>5.972222222222222</v>
       </c>
       <c r="L7">
-        <v>5.86875</v>
+        <v>6.05625</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -738,34 +747,34 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>6.1875</v>
+        <v>6.055555555555555</v>
       </c>
       <c r="D8">
-        <v>5.936170212765957</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="E8">
-        <v>5.761904761904762</v>
+        <v>5.880952380952381</v>
       </c>
       <c r="F8">
-        <v>5.894736842105263</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="G8">
-        <v>4.875</v>
+        <v>3.944444444444445</v>
       </c>
       <c r="H8">
-        <v>5.893617021276595</v>
+        <v>5.821428571428571</v>
       </c>
       <c r="I8">
-        <v>5.702380952380953</v>
+        <v>6.154761904761905</v>
       </c>
       <c r="J8">
-        <v>6.157894736842105</v>
+        <v>6.895833333333333</v>
       </c>
       <c r="K8">
-        <v>5.5</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="L8">
-        <v>6.175531914893617</v>
+        <v>6.065476190476191</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -776,34 +785,34 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>6.125</v>
+        <v>6.5</v>
       </c>
       <c r="D9">
-        <v>5.822222222222222</v>
+        <v>6.25</v>
       </c>
       <c r="E9">
-        <v>6.081395348837209</v>
+        <v>6.25</v>
       </c>
       <c r="F9">
-        <v>6.204545454545454</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G9">
-        <v>4.5625</v>
+        <v>5.5</v>
       </c>
       <c r="H9">
-        <v>5.822222222222222</v>
+        <v>6.25</v>
       </c>
       <c r="I9">
-        <v>6.558139534883721</v>
+        <v>6.75</v>
       </c>
       <c r="J9">
-        <v>6.886363636363637</v>
+        <v>7.5</v>
       </c>
       <c r="K9">
-        <v>4.9375</v>
+        <v>6.25</v>
       </c>
       <c r="L9">
-        <v>6.1</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -817,31 +826,31 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>5.894736842105263</v>
+        <v>5.836956521739131</v>
       </c>
       <c r="E10">
-        <v>6.078947368421052</v>
+        <v>5.7875</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>5.857142857142857</v>
       </c>
       <c r="G10">
-        <v>4.375</v>
+        <v>4.125</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>5.858695652173913</v>
       </c>
       <c r="I10">
-        <v>6.355263157894737</v>
+        <v>5.9625</v>
       </c>
       <c r="J10">
-        <v>6.318181818181818</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K10">
-        <v>4.65625</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
-        <v>6.289473684210527</v>
+        <v>6.108695652173913</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -852,34 +861,34 @@
         <v>20</v>
       </c>
       <c r="C11">
-        <v>6.142857142857143</v>
+        <v>6.4375</v>
       </c>
       <c r="D11">
-        <v>5.7875</v>
+        <v>5.848837209302325</v>
       </c>
       <c r="E11">
-        <v>5.743243243243243</v>
+        <v>5.930232558139535</v>
       </c>
       <c r="F11">
-        <v>6.033333333333333</v>
+        <v>6.047619047619047</v>
       </c>
       <c r="G11">
-        <v>4.285714285714286</v>
+        <v>6.0625</v>
       </c>
       <c r="H11">
-        <v>5.825</v>
+        <v>5.755813953488372</v>
       </c>
       <c r="I11">
-        <v>5.810810810810811</v>
+        <v>6.093023255813954</v>
       </c>
       <c r="J11">
-        <v>6.233333333333333</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K11">
-        <v>4.714285714285714</v>
+        <v>6.8125</v>
       </c>
       <c r="L11">
-        <v>6.08125</v>
+        <v>6.069767441860465</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -890,34 +899,34 @@
         <v>21</v>
       </c>
       <c r="C12">
-        <v>6.0625</v>
+        <v>6.3125</v>
       </c>
       <c r="D12">
-        <v>5.964285714285714</v>
+        <v>5.727272727272728</v>
       </c>
       <c r="E12">
-        <v>6.085365853658536</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>6.261904761904762</v>
+        <v>6.176470588235294</v>
       </c>
       <c r="G12">
-        <v>4.875</v>
+        <v>4.25</v>
       </c>
       <c r="H12">
-        <v>5.892857142857143</v>
+        <v>5.784090909090909</v>
       </c>
       <c r="I12">
-        <v>6.402439024390244</v>
+        <v>6.195652173913044</v>
       </c>
       <c r="J12">
-        <v>7.595238095238095</v>
+        <v>6.823529411764706</v>
       </c>
       <c r="K12">
-        <v>5.1875</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>6.238095238095238</v>
+        <v>6.085227272727272</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -928,34 +937,34 @@
         <v>22</v>
       </c>
       <c r="C13">
-        <v>6.166666666666667</v>
+        <v>6.055555555555555</v>
       </c>
       <c r="D13">
-        <v>6.127906976744186</v>
+        <v>6.025</v>
       </c>
       <c r="E13">
-        <v>6.22093023255814</v>
+        <v>6.078947368421052</v>
       </c>
       <c r="F13">
-        <v>6.444444444444445</v>
+        <v>6.239130434782608</v>
       </c>
       <c r="G13">
         <v>5.5</v>
       </c>
       <c r="H13">
-        <v>6.325581395348837</v>
+        <v>6.0125</v>
       </c>
       <c r="I13">
-        <v>6.906976744186046</v>
+        <v>6.263157894736842</v>
       </c>
       <c r="J13">
-        <v>7.666666666666667</v>
+        <v>7.043478260869565</v>
       </c>
       <c r="K13">
-        <v>6.027777777777778</v>
+        <v>5.805555555555555</v>
       </c>
       <c r="L13">
-        <v>6.767441860465116</v>
+        <v>6.3875</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -966,34 +975,34 @@
         <v>23</v>
       </c>
       <c r="C14">
-        <v>6.571428571428571</v>
+        <v>5.9</v>
       </c>
       <c r="D14">
-        <v>6.04054054054054</v>
+        <v>6.1</v>
       </c>
       <c r="E14">
-        <v>6.069444444444445</v>
+        <v>6.174418604651163</v>
       </c>
       <c r="F14">
-        <v>6.475</v>
+        <v>6.305555555555555</v>
       </c>
       <c r="G14">
-        <v>5.428571428571429</v>
+        <v>5</v>
       </c>
       <c r="H14">
-        <v>6.013513513513513</v>
+        <v>6.275</v>
       </c>
       <c r="I14">
-        <v>6.416666666666667</v>
+        <v>6.976744186046512</v>
       </c>
       <c r="J14">
-        <v>7.625</v>
+        <v>7.527777777777778</v>
       </c>
       <c r="K14">
-        <v>6.428571428571429</v>
+        <v>5.2</v>
       </c>
       <c r="L14">
-        <v>6.452702702702703</v>
+        <v>6.66875</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1004,34 +1013,34 @@
         <v>24</v>
       </c>
       <c r="C15">
-        <v>6.1875</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>5.918604651162791</v>
+        <v>5.709302325581396</v>
       </c>
       <c r="E15">
-        <v>6.182926829268292</v>
+        <v>5.952380952380953</v>
       </c>
       <c r="F15">
-        <v>6.086956521739131</v>
+        <v>5.928571428571429</v>
       </c>
       <c r="G15">
-        <v>5.3125</v>
+        <v>4.75</v>
       </c>
       <c r="H15">
-        <v>5.906976744186046</v>
+        <v>5.732558139534884</v>
       </c>
       <c r="I15">
-        <v>6.646341463414634</v>
+        <v>6.178571428571429</v>
       </c>
       <c r="J15">
-        <v>6.521739130434782</v>
+        <v>6.571428571428571</v>
       </c>
       <c r="K15">
-        <v>5.8125</v>
+        <v>5.03125</v>
       </c>
       <c r="L15">
-        <v>6.197674418604652</v>
+        <v>6.017441860465116</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1042,34 +1051,34 @@
         <v>25</v>
       </c>
       <c r="C16">
-        <v>6.214285714285714</v>
+        <v>5.944444444444445</v>
       </c>
       <c r="D16">
-        <v>5.803030303030303</v>
+        <v>5.622222222222222</v>
       </c>
       <c r="E16">
-        <v>5.906976744186046</v>
+        <v>5.897435897435898</v>
       </c>
       <c r="F16">
-        <v>6.078947368421052</v>
+        <v>5.909090909090909</v>
       </c>
       <c r="G16">
-        <v>4.357142857142857</v>
+        <v>4.5</v>
       </c>
       <c r="H16">
-        <v>5.939393939393939</v>
+        <v>5.655555555555556</v>
       </c>
       <c r="I16">
-        <v>6.162790697674419</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="J16">
-        <v>6.657894736842105</v>
+        <v>6.636363636363637</v>
       </c>
       <c r="K16">
-        <v>4.857142857142857</v>
+        <v>4.944444444444445</v>
       </c>
       <c r="L16">
-        <v>6.25</v>
+        <v>5.888888888888889</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1080,34 +1089,34 @@
         <v>26</v>
       </c>
       <c r="C17">
-        <v>6.3125</v>
+        <v>6.0625</v>
       </c>
       <c r="D17">
-        <v>5.736842105263158</v>
+        <v>6.045454545454546</v>
       </c>
       <c r="E17">
-        <v>5.901960784313726</v>
+        <v>6.092105263157895</v>
       </c>
       <c r="F17">
-        <v>5.809523809523809</v>
+        <v>6.391304347826087</v>
       </c>
       <c r="G17">
-        <v>5.1875</v>
+        <v>3.8125</v>
       </c>
       <c r="H17">
-        <v>5.631578947368421</v>
+        <v>6.318181818181818</v>
       </c>
       <c r="I17">
-        <v>6.068627450980392</v>
+        <v>6.223684210526316</v>
       </c>
       <c r="J17">
-        <v>6.190476190476191</v>
+        <v>7.739130434782608</v>
       </c>
       <c r="K17">
-        <v>5.78125</v>
+        <v>4.34375</v>
       </c>
       <c r="L17">
-        <v>5.881578947368421</v>
+        <v>6.857954545454546</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1118,34 +1127,34 @@
         <v>27</v>
       </c>
       <c r="C18">
-        <v>6.375</v>
+        <v>6.5</v>
       </c>
       <c r="D18">
-        <v>5.953488372093023</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="E18">
-        <v>5.841463414634147</v>
+        <v>5.9</v>
       </c>
       <c r="F18">
-        <v>6.04</v>
+        <v>5.5</v>
       </c>
       <c r="G18">
-        <v>5.625</v>
+        <v>5.5</v>
       </c>
       <c r="H18">
-        <v>5.883720930232558</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>5.975609756097561</v>
+        <v>5.9</v>
       </c>
       <c r="J18">
-        <v>6.46</v>
+        <v>5.5</v>
       </c>
       <c r="K18">
-        <v>6.3125</v>
+        <v>6.25</v>
       </c>
       <c r="L18">
-        <v>6.174418604651163</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1156,34 +1165,34 @@
         <v>28</v>
       </c>
       <c r="C19">
-        <v>6.4375</v>
+        <v>5.9375</v>
       </c>
       <c r="D19">
-        <v>5.813953488372093</v>
+        <v>6.058139534883721</v>
       </c>
       <c r="E19">
-        <v>5.877777777777778</v>
+        <v>6.177777777777778</v>
       </c>
       <c r="F19">
-        <v>5.833333333333333</v>
+        <v>6.159090909090909</v>
       </c>
       <c r="G19">
-        <v>5.1875</v>
+        <v>4.8125</v>
       </c>
       <c r="H19">
-        <v>5.918604651162791</v>
+        <v>6.255813953488372</v>
       </c>
       <c r="I19">
-        <v>6.144444444444445</v>
+        <v>6.7</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>7.159090909090909</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>5.03125</v>
       </c>
       <c r="L19">
-        <v>6.203488372093023</v>
+        <v>6.761627906976744</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1194,34 +1203,34 @@
         <v>29</v>
       </c>
       <c r="C20">
-        <v>6.4375</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>5.77906976744186</v>
+        <v>5.511627906976744</v>
       </c>
       <c r="E20">
-        <v>5.947368421052632</v>
+        <v>5.686046511627907</v>
       </c>
       <c r="F20">
-        <v>6.018518518518518</v>
+        <v>5.739130434782608</v>
       </c>
       <c r="G20">
-        <v>4.6875</v>
+        <v>3.625</v>
       </c>
       <c r="H20">
-        <v>5.72093023255814</v>
+        <v>5.453488372093023</v>
       </c>
       <c r="I20">
-        <v>5.960526315789473</v>
+        <v>5.906976744186046</v>
       </c>
       <c r="J20">
-        <v>6.537037037037037</v>
+        <v>6.130434782608695</v>
       </c>
       <c r="K20">
-        <v>5.40625</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>5.994186046511628</v>
+        <v>5.598837209302325</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1232,34 +1241,148 @@
         <v>30</v>
       </c>
       <c r="C21">
+        <v>6.5625</v>
+      </c>
+      <c r="D21">
+        <v>6.141025641025641</v>
+      </c>
+      <c r="E21">
+        <v>6.134146341463414</v>
+      </c>
+      <c r="F21">
+        <v>6.293103448275862</v>
+      </c>
+      <c r="G21">
         <v>6.0625</v>
       </c>
-      <c r="D21">
-        <v>6.065789473684211</v>
-      </c>
-      <c r="E21">
-        <v>6.166666666666667</v>
-      </c>
-      <c r="F21">
-        <v>6.166666666666667</v>
-      </c>
-      <c r="G21">
-        <v>5.0625</v>
-      </c>
       <c r="H21">
-        <v>6.236842105263158</v>
+        <v>6.32051282051282</v>
       </c>
       <c r="I21">
-        <v>6.619047619047619</v>
+        <v>6.26829268292683</v>
       </c>
       <c r="J21">
-        <v>7.083333333333333</v>
+        <v>7.258620689655173</v>
       </c>
       <c r="K21">
-        <v>5.40625</v>
+        <v>7.03125</v>
       </c>
       <c r="L21">
-        <v>6.736842105263158</v>
+        <v>6.942307692307693</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>6.1875</v>
+      </c>
+      <c r="D22">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="E22">
+        <v>6.046511627906977</v>
+      </c>
+      <c r="F22">
+        <v>6.15</v>
+      </c>
+      <c r="G22">
+        <v>5.5625</v>
+      </c>
+      <c r="H22">
+        <v>5.845238095238095</v>
+      </c>
+      <c r="I22">
+        <v>6.244186046511628</v>
+      </c>
+      <c r="J22">
+        <v>6.625</v>
+      </c>
+      <c r="K22">
+        <v>6</v>
+      </c>
+      <c r="L22">
+        <v>6.154761904761905</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>6.25</v>
+      </c>
+      <c r="D23">
+        <v>6.046511627906977</v>
+      </c>
+      <c r="E23">
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <v>5.92</v>
+      </c>
+      <c r="G23">
+        <v>5.75</v>
+      </c>
+      <c r="H23">
+        <v>6.058139534883721</v>
+      </c>
+      <c r="I23">
+        <v>6.328571428571428</v>
+      </c>
+      <c r="J23">
+        <v>6.2</v>
+      </c>
+      <c r="K23">
+        <v>6.28125</v>
+      </c>
+      <c r="L23">
+        <v>6.459302325581396</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>6.5</v>
+      </c>
+      <c r="D24">
+        <v>5.972972972972973</v>
+      </c>
+      <c r="E24">
+        <v>5.895833333333333</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <v>4.9375</v>
+      </c>
+      <c r="H24">
+        <v>6.202702702702703</v>
+      </c>
+      <c r="I24">
+        <v>5.84375</v>
+      </c>
+      <c r="J24">
+        <v>6.238095238095238</v>
+      </c>
+      <c r="K24">
+        <v>5.8125</v>
+      </c>
+      <c r="L24">
+        <v>6.716216216216216</v>
       </c>
     </row>
   </sheetData>

--- a/voti_contro.xlsx
+++ b/voti_contro.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>squadra</t>
   </si>
@@ -49,45 +49,60 @@
     <t>MediaConMod_D</t>
   </si>
   <si>
+    <t>GENOA</t>
+  </si>
+  <si>
+    <t>VERONA</t>
+  </si>
+  <si>
     <t>EMPOLI</t>
   </si>
   <si>
     <t>JUVENTUS</t>
   </si>
   <si>
-    <t>VERONA</t>
-  </si>
-  <si>
-    <t>GENOA</t>
+    <t>PARMA</t>
+  </si>
+  <si>
+    <t>MILAN</t>
+  </si>
+  <si>
+    <t>SASSUOLO</t>
+  </si>
+  <si>
+    <t>FIORENTINA</t>
+  </si>
+  <si>
+    <t>VENEZIA</t>
+  </si>
+  <si>
+    <t>LECCE</t>
   </si>
   <si>
     <t>TORINO</t>
   </si>
   <si>
-    <t>FIORENTINA</t>
-  </si>
-  <si>
-    <t>LECCE</t>
+    <t>ATALANTA</t>
+  </si>
+  <si>
+    <t>NAPOLI</t>
+  </si>
+  <si>
+    <t>UDINESE</t>
+  </si>
+  <si>
+    <t>COMO</t>
+  </si>
+  <si>
+    <t>BOLOGNA</t>
+  </si>
+  <si>
+    <t>CAGLIARI</t>
   </si>
   <si>
     <t>ROMA</t>
   </si>
   <si>
-    <t>BOLOGNA</t>
-  </si>
-  <si>
-    <t>CAGLIARI</t>
-  </si>
-  <si>
-    <t>UDINESE</t>
-  </si>
-  <si>
-    <t>ATALANTA</t>
-  </si>
-  <si>
-    <t>NAPOLI</t>
-  </si>
-  <si>
     <t>INTER</t>
   </si>
   <si>
@@ -95,12 +110,6 @@
   </si>
   <si>
     <t>SALERNITANA</t>
-  </si>
-  <si>
-    <t>MILAN</t>
-  </si>
-  <si>
-    <t>SASSUOLO</t>
   </si>
   <si>
     <t>LAZIO</t>
@@ -464,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -510,34 +519,34 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>6.125</v>
+        <v>6.0625</v>
       </c>
       <c r="D2">
-        <v>6.184782608695652</v>
+        <v>5.697674418604652</v>
       </c>
       <c r="E2">
-        <v>6.075757575757576</v>
+        <v>5.952380952380953</v>
       </c>
       <c r="F2">
-        <v>6.0625</v>
+        <v>5.977272727272728</v>
       </c>
       <c r="G2">
-        <v>5.5</v>
+        <v>4.8125</v>
       </c>
       <c r="H2">
-        <v>6.326086956521739</v>
+        <v>5.709302325581396</v>
       </c>
       <c r="I2">
-        <v>6.348484848484849</v>
+        <v>6.190476190476191</v>
       </c>
       <c r="J2">
-        <v>6.708333333333333</v>
+        <v>6.75</v>
       </c>
       <c r="K2">
-        <v>5.9375</v>
+        <v>5.15625</v>
       </c>
       <c r="L2">
-        <v>6.831521739130435</v>
+        <v>5.994186046511628</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -548,34 +557,34 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>6.5</v>
+        <v>5.8125</v>
       </c>
       <c r="D3">
-        <v>6.1</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="E3">
-        <v>6.054347826086956</v>
+        <v>5.9375</v>
       </c>
       <c r="F3">
-        <v>5.958333333333333</v>
+        <v>5.875</v>
       </c>
       <c r="G3">
-        <v>5.4375</v>
+        <v>4.3125</v>
       </c>
       <c r="H3">
-        <v>6.457142857142857</v>
+        <v>5.677777777777778</v>
       </c>
       <c r="I3">
-        <v>6.076086956521739</v>
+        <v>6.25</v>
       </c>
       <c r="J3">
-        <v>6.125</v>
+        <v>6.525</v>
       </c>
       <c r="K3">
-        <v>6.3125</v>
+        <v>4.6875</v>
       </c>
       <c r="L3">
-        <v>7.05</v>
+        <v>5.955555555555556</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -586,34 +595,34 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>5.8125</v>
+        <v>6.1875</v>
       </c>
       <c r="D4">
-        <v>5.790697674418604</v>
+        <v>6.102272727272728</v>
       </c>
       <c r="E4">
-        <v>6.034090909090909</v>
+        <v>5.955882352941177</v>
       </c>
       <c r="F4">
-        <v>5.921052631578948</v>
+        <v>5.979166666666667</v>
       </c>
       <c r="G4">
-        <v>4.5625</v>
+        <v>5.5625</v>
       </c>
       <c r="H4">
-        <v>5.802325581395348</v>
+        <v>6.136363636363637</v>
       </c>
       <c r="I4">
-        <v>6.386363636363637</v>
+        <v>6.205882352941177</v>
       </c>
       <c r="J4">
-        <v>6.631578947368421</v>
+        <v>6.5</v>
       </c>
       <c r="K4">
-        <v>4.9375</v>
+        <v>6.0625</v>
       </c>
       <c r="L4">
-        <v>6.081395348837209</v>
+        <v>6.5625</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -624,34 +633,34 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>6.1875</v>
+        <v>6.5</v>
       </c>
       <c r="D5">
-        <v>5.73170731707317</v>
+        <v>5.957142857142857</v>
       </c>
       <c r="E5">
-        <v>5.964285714285714</v>
+        <v>5.978723404255319</v>
       </c>
       <c r="F5">
-        <v>5.928571428571429</v>
+        <v>5.916666666666667</v>
       </c>
       <c r="G5">
-        <v>4.6875</v>
+        <v>5.0625</v>
       </c>
       <c r="H5">
-        <v>5.75609756097561</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
-        <v>6.238095238095238</v>
+        <v>5.957446808510638</v>
       </c>
       <c r="J5">
-        <v>6.452380952380953</v>
+        <v>6.104166666666667</v>
       </c>
       <c r="K5">
-        <v>5.125</v>
+        <v>5.9375</v>
       </c>
       <c r="L5">
-        <v>6.048780487804878</v>
+        <v>6.714285714285714</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -662,34 +671,34 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>6.1875</v>
+        <v>6.5</v>
       </c>
       <c r="D6">
-        <v>5.878048780487805</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="E6">
-        <v>5.963414634146342</v>
+        <v>5.9</v>
       </c>
       <c r="F6">
-        <v>6.041666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="G6">
-        <v>5.1875</v>
+        <v>5.5</v>
       </c>
       <c r="H6">
-        <v>5.804878048780488</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>6.195121951219512</v>
+        <v>5.9</v>
       </c>
       <c r="J6">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K6">
-        <v>5.6875</v>
+        <v>6.25</v>
       </c>
       <c r="L6">
-        <v>6.140243902439025</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -700,34 +709,34 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>6.3125</v>
+        <v>6.25</v>
       </c>
       <c r="D7">
-        <v>5.837209302325581</v>
+        <v>5.977272727272728</v>
       </c>
       <c r="E7">
-        <v>5.953488372093023</v>
+        <v>6.071428571428571</v>
       </c>
       <c r="F7">
-        <v>6.113636363636363</v>
+        <v>6.192307692307693</v>
       </c>
       <c r="G7">
-        <v>4.5625</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>5.918604651162791</v>
+        <v>6.170454545454546</v>
       </c>
       <c r="I7">
-        <v>6.197674418604652</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
-        <v>6.704545454545454</v>
+        <v>7.115384615384615</v>
       </c>
       <c r="K7">
-        <v>5.25</v>
+        <v>4.53125</v>
       </c>
       <c r="L7">
-        <v>6.215116279069767</v>
+        <v>6.647727272727272</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -738,34 +747,34 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>6.375</v>
+        <v>5.9375</v>
       </c>
       <c r="D8">
-        <v>5.888888888888889</v>
+        <v>6.097560975609756</v>
       </c>
       <c r="E8">
-        <v>5.920454545454546</v>
+        <v>6.174418604651163</v>
       </c>
       <c r="F8">
-        <v>5.954545454545454</v>
+        <v>6.227272727272728</v>
       </c>
       <c r="G8">
-        <v>5.5625</v>
+        <v>4.8125</v>
       </c>
       <c r="H8">
-        <v>5.9</v>
+        <v>6.292682926829269</v>
       </c>
       <c r="I8">
-        <v>6.193181818181818</v>
+        <v>6.709302325581396</v>
       </c>
       <c r="J8">
-        <v>6.477272727272728</v>
+        <v>7.340909090909091</v>
       </c>
       <c r="K8">
-        <v>6.21875</v>
+        <v>5.03125</v>
       </c>
       <c r="L8">
-        <v>6.233333333333333</v>
+        <v>6.829268292682927</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -776,34 +785,34 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>6.1875</v>
+        <v>6.125</v>
       </c>
       <c r="D9">
-        <v>5.9875</v>
+        <v>5.880952380952381</v>
       </c>
       <c r="E9">
-        <v>6.135135135135135</v>
+        <v>5.897727272727272</v>
       </c>
       <c r="F9">
-        <v>6.104166666666667</v>
+        <v>6.065217391304348</v>
       </c>
       <c r="G9">
-        <v>5.0625</v>
+        <v>4.375</v>
       </c>
       <c r="H9">
-        <v>6.1125</v>
+        <v>5.964285714285714</v>
       </c>
       <c r="I9">
-        <v>6.486486486486487</v>
+        <v>6.113636363636363</v>
       </c>
       <c r="J9">
-        <v>6.395833333333333</v>
+        <v>6.5</v>
       </c>
       <c r="K9">
-        <v>5.5</v>
+        <v>4.875</v>
       </c>
       <c r="L9">
-        <v>6.4875</v>
+        <v>6.297619047619047</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -814,34 +823,34 @@
         <v>19</v>
       </c>
       <c r="C10">
-        <v>6.0625</v>
+        <v>6.5</v>
       </c>
       <c r="D10">
-        <v>5.738095238095238</v>
+        <v>6.25</v>
       </c>
       <c r="E10">
-        <v>5.707317073170731</v>
+        <v>6.25</v>
       </c>
       <c r="F10">
-        <v>5.975</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G10">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="H10">
-        <v>5.571428571428571</v>
+        <v>6.25</v>
       </c>
       <c r="I10">
-        <v>5.573170731707317</v>
+        <v>6.75</v>
       </c>
       <c r="J10">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="L10">
-        <v>5.779761904761905</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -852,34 +861,34 @@
         <v>20</v>
       </c>
       <c r="C11">
-        <v>6.125</v>
+        <v>6.3125</v>
       </c>
       <c r="D11">
-        <v>5.840425531914893</v>
+        <v>5.967391304347826</v>
       </c>
       <c r="E11">
-        <v>6.089743589743589</v>
+        <v>6.060975609756097</v>
       </c>
       <c r="F11">
-        <v>6.28</v>
+        <v>6.065217391304348</v>
       </c>
       <c r="G11">
-        <v>4.6875</v>
+        <v>5.5</v>
       </c>
       <c r="H11">
-        <v>5.840425531914893</v>
+        <v>6.010869565217392</v>
       </c>
       <c r="I11">
-        <v>6.653846153846154</v>
+        <v>6.512195121951219</v>
       </c>
       <c r="J11">
-        <v>7.18</v>
+        <v>6.826086956521739</v>
       </c>
       <c r="K11">
-        <v>5.0625</v>
+        <v>6.09375</v>
       </c>
       <c r="L11">
-        <v>6.101063829787234</v>
+        <v>6.402173913043478</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -890,34 +899,34 @@
         <v>21</v>
       </c>
       <c r="C12">
-        <v>6.0625</v>
+        <v>6.1875</v>
       </c>
       <c r="D12">
-        <v>5.895348837209302</v>
+        <v>5.82051282051282</v>
       </c>
       <c r="E12">
-        <v>6.071428571428571</v>
+        <v>5.987804878048781</v>
       </c>
       <c r="F12">
-        <v>6.181818181818182</v>
+        <v>6.038461538461538</v>
       </c>
       <c r="G12">
         <v>5.0625</v>
       </c>
       <c r="H12">
-        <v>5.86046511627907</v>
+        <v>5.705128205128205</v>
       </c>
       <c r="I12">
-        <v>6.369047619047619</v>
+        <v>6.26829268292683</v>
       </c>
       <c r="J12">
-        <v>6.727272727272728</v>
+        <v>6.653846153846154</v>
       </c>
       <c r="K12">
-        <v>5.40625</v>
+        <v>5.5625</v>
       </c>
       <c r="L12">
-        <v>6.133720930232558</v>
+        <v>6.044871794871795</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -931,31 +940,31 @@
         <v>6.1875</v>
       </c>
       <c r="D13">
-        <v>5.634146341463414</v>
+        <v>5.595238095238095</v>
       </c>
       <c r="E13">
-        <v>5.797872340425532</v>
+        <v>5.804347826086956</v>
       </c>
       <c r="F13">
-        <v>5.863636363636363</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G13">
-        <v>4.1875</v>
+        <v>4.0625</v>
       </c>
       <c r="H13">
-        <v>5.658536585365853</v>
+        <v>5.630952380952381</v>
       </c>
       <c r="I13">
-        <v>6.074468085106383</v>
+        <v>6.086956521739131</v>
       </c>
       <c r="J13">
-        <v>6.090909090909091</v>
+        <v>6.095238095238095</v>
       </c>
       <c r="K13">
-        <v>4.6875</v>
+        <v>4.5625</v>
       </c>
       <c r="L13">
-        <v>5.853658536585366</v>
+        <v>5.827380952380953</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -966,34 +975,34 @@
         <v>23</v>
       </c>
       <c r="C14">
-        <v>6.5</v>
+        <v>6.4375</v>
       </c>
       <c r="D14">
-        <v>6.130952380952381</v>
+        <v>6.128205128205129</v>
       </c>
       <c r="E14">
-        <v>6.158536585365853</v>
+        <v>6.13953488372093</v>
       </c>
       <c r="F14">
-        <v>6.384615384615385</v>
+        <v>6.37037037037037</v>
       </c>
       <c r="G14">
-        <v>5.5</v>
+        <v>5.4375</v>
       </c>
       <c r="H14">
-        <v>6.321428571428571</v>
+        <v>6.294871794871795</v>
       </c>
       <c r="I14">
-        <v>6.512195121951219</v>
+        <v>6.348837209302325</v>
       </c>
       <c r="J14">
-        <v>7.346153846153846</v>
+        <v>7.518518518518518</v>
       </c>
       <c r="K14">
-        <v>6.46875</v>
+        <v>6.3125</v>
       </c>
       <c r="L14">
-        <v>6.898809523809524</v>
+        <v>6.897435897435898</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1004,34 +1013,34 @@
         <v>24</v>
       </c>
       <c r="C15">
-        <v>6.1875</v>
+        <v>6.125</v>
       </c>
       <c r="D15">
-        <v>5.782608695652174</v>
+        <v>5.918604651162791</v>
       </c>
       <c r="E15">
-        <v>5.837209302325581</v>
+        <v>6.113636363636363</v>
       </c>
       <c r="F15">
-        <v>6.058823529411764</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="G15">
-        <v>4.1875</v>
+        <v>5.5</v>
       </c>
       <c r="H15">
-        <v>5.771739130434782</v>
+        <v>5.895348837209302</v>
       </c>
       <c r="I15">
-        <v>6.011627906976744</v>
+        <v>6.443181818181818</v>
       </c>
       <c r="J15">
-        <v>6.441176470588236</v>
+        <v>6.595238095238095</v>
       </c>
       <c r="K15">
-        <v>4.71875</v>
+        <v>5.90625</v>
       </c>
       <c r="L15">
-        <v>6.076086956521739</v>
+        <v>6.197674418604652</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1045,31 +1054,31 @@
         <v>6</v>
       </c>
       <c r="D16">
-        <v>5.95</v>
+        <v>6.3</v>
       </c>
       <c r="E16">
-        <v>6.141025641025641</v>
+        <v>6.4</v>
       </c>
       <c r="F16">
-        <v>6.282608695652174</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="G16">
-        <v>5.125</v>
+        <v>6</v>
       </c>
       <c r="H16">
-        <v>5.8625</v>
+        <v>6.8</v>
       </c>
       <c r="I16">
-        <v>6.487179487179487</v>
+        <v>6.9</v>
       </c>
       <c r="J16">
-        <v>7.391304347826087</v>
+        <v>8.5</v>
       </c>
       <c r="K16">
-        <v>5.375</v>
+        <v>6.25</v>
       </c>
       <c r="L16">
-        <v>6.1625</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1080,34 +1089,34 @@
         <v>26</v>
       </c>
       <c r="C17">
-        <v>6.055555555555555</v>
+        <v>6.25</v>
       </c>
       <c r="D17">
-        <v>6.131578947368421</v>
+        <v>5.841463414634147</v>
       </c>
       <c r="E17">
-        <v>6.25531914893617</v>
+        <v>5.723684210526316</v>
       </c>
       <c r="F17">
-        <v>6.222222222222222</v>
+        <v>5.863636363636363</v>
       </c>
       <c r="G17">
-        <v>5.388888888888889</v>
+        <v>4.875</v>
       </c>
       <c r="H17">
-        <v>6.315789473684211</v>
+        <v>5.73170731707317</v>
       </c>
       <c r="I17">
-        <v>7.117021276595745</v>
+        <v>5.605263157894737</v>
       </c>
       <c r="J17">
-        <v>7.111111111111111</v>
+        <v>6.227272727272728</v>
       </c>
       <c r="K17">
-        <v>5.694444444444445</v>
+        <v>5.5625</v>
       </c>
       <c r="L17">
-        <v>6.75</v>
+        <v>6.036585365853658</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1118,34 +1127,34 @@
         <v>27</v>
       </c>
       <c r="C18">
-        <v>6.3125</v>
+        <v>6.125</v>
       </c>
       <c r="D18">
-        <v>5.895348837209302</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="E18">
-        <v>6.088235294117647</v>
+        <v>6.135135135135135</v>
       </c>
       <c r="F18">
-        <v>6.134615384615385</v>
+        <v>6.211538461538462</v>
       </c>
       <c r="G18">
-        <v>4.0625</v>
+        <v>4.8125</v>
       </c>
       <c r="H18">
-        <v>6.058139534883721</v>
+        <v>5.84375</v>
       </c>
       <c r="I18">
-        <v>6.338235294117647</v>
+        <v>6.743243243243243</v>
       </c>
       <c r="J18">
-        <v>6.980769230769231</v>
+        <v>6.923076923076923</v>
       </c>
       <c r="K18">
-        <v>4.6875</v>
+        <v>5.1875</v>
       </c>
       <c r="L18">
-        <v>6.453488372093023</v>
+        <v>6.098958333333333</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1156,34 +1165,34 @@
         <v>28</v>
       </c>
       <c r="C19">
-        <v>5.9375</v>
+        <v>6.1875</v>
       </c>
       <c r="D19">
-        <v>6.097560975609756</v>
+        <v>5.9625</v>
       </c>
       <c r="E19">
-        <v>6.174418604651163</v>
+        <v>6.118421052631579</v>
       </c>
       <c r="F19">
-        <v>6.227272727272728</v>
+        <v>6.113636363636363</v>
       </c>
       <c r="G19">
-        <v>4.8125</v>
+        <v>5.0625</v>
       </c>
       <c r="H19">
-        <v>6.292682926829269</v>
+        <v>6.0875</v>
       </c>
       <c r="I19">
-        <v>6.709302325581396</v>
+        <v>6.460526315789473</v>
       </c>
       <c r="J19">
-        <v>7.340909090909091</v>
+        <v>6.454545454545454</v>
       </c>
       <c r="K19">
-        <v>5.03125</v>
+        <v>5.5</v>
       </c>
       <c r="L19">
-        <v>6.829268292682927</v>
+        <v>6.4375</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1194,34 +1203,34 @@
         <v>29</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>6.125</v>
       </c>
       <c r="D20">
-        <v>5.920454545454546</v>
+        <v>5.797872340425532</v>
       </c>
       <c r="E20">
-        <v>5.75</v>
+        <v>5.943181818181818</v>
       </c>
       <c r="F20">
-        <v>5.909090909090909</v>
+        <v>6.0625</v>
       </c>
       <c r="G20">
-        <v>4.5</v>
+        <v>4.0625</v>
       </c>
       <c r="H20">
-        <v>5.988636363636363</v>
+        <v>5.861702127659575</v>
       </c>
       <c r="I20">
-        <v>5.785714285714286</v>
+        <v>6.113636363636363</v>
       </c>
       <c r="J20">
-        <v>6.227272727272728</v>
+        <v>6.5</v>
       </c>
       <c r="K20">
-        <v>4.84375</v>
+        <v>4.53125</v>
       </c>
       <c r="L20">
-        <v>6.289772727272728</v>
+        <v>6.196808510638298</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1232,33 +1241,147 @@
         <v>30</v>
       </c>
       <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>5.9625</v>
+      </c>
+      <c r="E21">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="F21">
+        <v>6.282608695652174</v>
+      </c>
+      <c r="G21">
+        <v>5.125</v>
+      </c>
+      <c r="H21">
+        <v>5.875</v>
+      </c>
+      <c r="I21">
+        <v>6.5</v>
+      </c>
+      <c r="J21">
+        <v>7.260869565217392</v>
+      </c>
+      <c r="K21">
+        <v>5.375</v>
+      </c>
+      <c r="L21">
+        <v>6.18125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>6.055555555555555</v>
+      </c>
+      <c r="D22">
+        <v>6.131578947368421</v>
+      </c>
+      <c r="E22">
+        <v>6.25531914893617</v>
+      </c>
+      <c r="F22">
+        <v>6.222222222222222</v>
+      </c>
+      <c r="G22">
+        <v>5.388888888888889</v>
+      </c>
+      <c r="H22">
+        <v>6.315789473684211</v>
+      </c>
+      <c r="I22">
+        <v>7.117021276595745</v>
+      </c>
+      <c r="J22">
+        <v>7.111111111111111</v>
+      </c>
+      <c r="K22">
+        <v>5.694444444444445</v>
+      </c>
+      <c r="L22">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>6.0625</v>
+      </c>
+      <c r="D23">
+        <v>5.855555555555555</v>
+      </c>
+      <c r="E23">
+        <v>5.8125</v>
+      </c>
+      <c r="F23">
+        <v>5.880952380952381</v>
+      </c>
+      <c r="G23">
+        <v>4.3125</v>
+      </c>
+      <c r="H23">
+        <v>5.855555555555555</v>
+      </c>
+      <c r="I23">
+        <v>5.975</v>
+      </c>
+      <c r="J23">
+        <v>6.214285714285714</v>
+      </c>
+      <c r="K23">
+        <v>4.71875</v>
+      </c>
+      <c r="L23">
+        <v>6.122222222222222</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
         <v>6.3125</v>
       </c>
-      <c r="D21">
+      <c r="D24">
         <v>5.825581395348837</v>
       </c>
-      <c r="E21">
+      <c r="E24">
         <v>5.956521739130435</v>
       </c>
-      <c r="F21">
+      <c r="F24">
         <v>5.95</v>
       </c>
-      <c r="G21">
+      <c r="G24">
         <v>5.8125</v>
       </c>
-      <c r="H21">
+      <c r="H24">
         <v>5.744186046511628</v>
       </c>
-      <c r="I21">
+      <c r="I24">
         <v>6.163043478260869</v>
       </c>
-      <c r="J21">
+      <c r="J24">
         <v>6.575</v>
       </c>
-      <c r="K21">
+      <c r="K24">
         <v>6.40625</v>
       </c>
-      <c r="L21">
+      <c r="L24">
         <v>6.034883720930233</v>
       </c>
     </row>

--- a/voti_contro.xlsx
+++ b/voti_contro.xlsx
@@ -49,60 +49,66 @@
     <t>MediaConMod_D</t>
   </si>
   <si>
+    <t>EMPOLI</t>
+  </si>
+  <si>
+    <t>JUVENTUS</t>
+  </si>
+  <si>
+    <t>COMO</t>
+  </si>
+  <si>
+    <t>BOLOGNA</t>
+  </si>
+  <si>
+    <t>CAGLIARI</t>
+  </si>
+  <si>
+    <t>ROMA</t>
+  </si>
+  <si>
+    <t>NAPOLI</t>
+  </si>
+  <si>
+    <t>UDINESE</t>
+  </si>
+  <si>
+    <t>ATALANTA</t>
+  </si>
+  <si>
     <t>GENOA</t>
   </si>
   <si>
     <t>VERONA</t>
   </si>
   <si>
-    <t>EMPOLI</t>
-  </si>
-  <si>
-    <t>JUVENTUS</t>
+    <t>LAZIO</t>
+  </si>
+  <si>
+    <t>FROSINONE</t>
+  </si>
+  <si>
+    <t>LECCE</t>
+  </si>
+  <si>
+    <t>TORINO</t>
+  </si>
+  <si>
+    <t>FIORENTINA</t>
+  </si>
+  <si>
+    <t>VENEZIA</t>
+  </si>
+  <si>
+    <t>MILAN</t>
   </si>
   <si>
     <t>PARMA</t>
   </si>
   <si>
-    <t>MILAN</t>
-  </si>
-  <si>
     <t>SASSUOLO</t>
   </si>
   <si>
-    <t>FIORENTINA</t>
-  </si>
-  <si>
-    <t>VENEZIA</t>
-  </si>
-  <si>
-    <t>LECCE</t>
-  </si>
-  <si>
-    <t>TORINO</t>
-  </si>
-  <si>
-    <t>ATALANTA</t>
-  </si>
-  <si>
-    <t>NAPOLI</t>
-  </si>
-  <si>
-    <t>UDINESE</t>
-  </si>
-  <si>
-    <t>COMO</t>
-  </si>
-  <si>
-    <t>BOLOGNA</t>
-  </si>
-  <si>
-    <t>CAGLIARI</t>
-  </si>
-  <si>
-    <t>ROMA</t>
-  </si>
-  <si>
     <t>INTER</t>
   </si>
   <si>
@@ -110,12 +116,6 @@
   </si>
   <si>
     <t>SALERNITANA</t>
-  </si>
-  <si>
-    <t>LAZIO</t>
-  </si>
-  <si>
-    <t>FROSINONE</t>
   </si>
 </sst>
 </file>
@@ -519,34 +519,34 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>6.0625</v>
+        <v>6.25</v>
       </c>
       <c r="D2">
-        <v>5.697674418604652</v>
+        <v>6.011904761904762</v>
       </c>
       <c r="E2">
-        <v>5.952380952380953</v>
+        <v>5.918918918918919</v>
       </c>
       <c r="F2">
-        <v>5.977272727272728</v>
+        <v>5.78</v>
       </c>
       <c r="G2">
-        <v>4.8125</v>
+        <v>5.5</v>
       </c>
       <c r="H2">
-        <v>5.709302325581396</v>
+        <v>6.023809523809524</v>
       </c>
       <c r="I2">
-        <v>6.190476190476191</v>
+        <v>6.256756756756757</v>
       </c>
       <c r="J2">
-        <v>6.75</v>
+        <v>6.04</v>
       </c>
       <c r="K2">
-        <v>5.15625</v>
+        <v>6.03125</v>
       </c>
       <c r="L2">
-        <v>5.994186046511628</v>
+        <v>6.398809523809524</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -557,34 +557,34 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>5.8125</v>
+        <v>6.4375</v>
       </c>
       <c r="D3">
-        <v>5.666666666666667</v>
+        <v>5.864864864864865</v>
       </c>
       <c r="E3">
-        <v>5.9375</v>
+        <v>5.84</v>
       </c>
       <c r="F3">
-        <v>5.875</v>
+        <v>5.952380952380953</v>
       </c>
       <c r="G3">
-        <v>4.3125</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
-        <v>5.677777777777778</v>
+        <v>6.108108108108108</v>
       </c>
       <c r="I3">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="J3">
-        <v>6.525</v>
+        <v>6.190476190476191</v>
       </c>
       <c r="K3">
-        <v>4.6875</v>
+        <v>5.3125</v>
       </c>
       <c r="L3">
-        <v>5.955555555555556</v>
+        <v>6.594594594594595</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -595,34 +595,34 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>6.1875</v>
+        <v>6.25</v>
       </c>
       <c r="D4">
-        <v>6.102272727272728</v>
+        <v>6.181818181818182</v>
       </c>
       <c r="E4">
-        <v>5.955882352941177</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="F4">
-        <v>5.979166666666667</v>
+        <v>6.583333333333333</v>
       </c>
       <c r="G4">
-        <v>5.5625</v>
+        <v>5.75</v>
       </c>
       <c r="H4">
-        <v>6.136363636363637</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
-        <v>6.205882352941177</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="J4">
-        <v>6.5</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="K4">
-        <v>6.0625</v>
+        <v>6.25</v>
       </c>
       <c r="L4">
-        <v>6.5625</v>
+        <v>6.977272727272728</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -633,34 +633,34 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>6.5</v>
+        <v>6.0625</v>
       </c>
       <c r="D5">
-        <v>5.957142857142857</v>
+        <v>5.930232558139535</v>
       </c>
       <c r="E5">
-        <v>5.978723404255319</v>
+        <v>5.855263157894737</v>
       </c>
       <c r="F5">
-        <v>5.916666666666667</v>
+        <v>6.086956521739131</v>
       </c>
       <c r="G5">
+        <v>4.625</v>
+      </c>
+      <c r="H5">
+        <v>5.930232558139535</v>
+      </c>
+      <c r="I5">
+        <v>5.894736842105263</v>
+      </c>
+      <c r="J5">
+        <v>6.869565217391305</v>
+      </c>
+      <c r="K5">
         <v>5.0625</v>
       </c>
-      <c r="H5">
-        <v>6.2</v>
-      </c>
-      <c r="I5">
-        <v>5.957446808510638</v>
-      </c>
-      <c r="J5">
-        <v>6.104166666666667</v>
-      </c>
-      <c r="K5">
-        <v>5.9375</v>
-      </c>
       <c r="L5">
-        <v>6.714285714285714</v>
+        <v>6.308139534883721</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -671,34 +671,34 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>6.5</v>
+        <v>6.125</v>
       </c>
       <c r="D6">
-        <v>5.714285714285714</v>
+        <v>5.852272727272728</v>
       </c>
       <c r="E6">
-        <v>5.9</v>
+        <v>6.146341463414634</v>
       </c>
       <c r="F6">
-        <v>5.5</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G6">
-        <v>5.5</v>
+        <v>4.9375</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>5.909090909090909</v>
       </c>
       <c r="I6">
-        <v>5.9</v>
+        <v>6.76829268292683</v>
       </c>
       <c r="J6">
-        <v>5.5</v>
+        <v>6.703703703703703</v>
       </c>
       <c r="K6">
-        <v>6.25</v>
+        <v>5.34375</v>
       </c>
       <c r="L6">
-        <v>6.25</v>
+        <v>6.170454545454546</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -712,31 +712,31 @@
         <v>6.25</v>
       </c>
       <c r="D7">
-        <v>5.977272727272728</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>6.071428571428571</v>
+        <v>6.135135135135135</v>
       </c>
       <c r="F7">
-        <v>6.192307692307693</v>
+        <v>6.270833333333333</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5.125</v>
       </c>
       <c r="H7">
-        <v>6.170454545454546</v>
+        <v>6.083333333333333</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>6.391891891891892</v>
       </c>
       <c r="J7">
-        <v>7.115384615384615</v>
+        <v>6.875</v>
       </c>
       <c r="K7">
-        <v>4.53125</v>
+        <v>5.625</v>
       </c>
       <c r="L7">
-        <v>6.647727272727272</v>
+        <v>6.452380952380953</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -747,34 +747,34 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>5.9375</v>
+        <v>6.4375</v>
       </c>
       <c r="D8">
-        <v>6.097560975609756</v>
+        <v>6.0875</v>
       </c>
       <c r="E8">
-        <v>6.174418604651163</v>
+        <v>6.081395348837209</v>
       </c>
       <c r="F8">
-        <v>6.227272727272728</v>
+        <v>6.214285714285714</v>
       </c>
       <c r="G8">
-        <v>4.8125</v>
+        <v>5.8125</v>
       </c>
       <c r="H8">
-        <v>6.292682926829269</v>
+        <v>6.225</v>
       </c>
       <c r="I8">
-        <v>6.709302325581396</v>
+        <v>6.209302325581396</v>
       </c>
       <c r="J8">
-        <v>7.340909090909091</v>
+        <v>7.107142857142857</v>
       </c>
       <c r="K8">
-        <v>5.03125</v>
+        <v>6.625</v>
       </c>
       <c r="L8">
-        <v>6.829268292682927</v>
+        <v>6.7875</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -785,34 +785,34 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>6.125</v>
+        <v>6.0625</v>
       </c>
       <c r="D9">
-        <v>5.880952380952381</v>
+        <v>5.773809523809524</v>
       </c>
       <c r="E9">
-        <v>5.897727272727272</v>
+        <v>5.963414634146342</v>
       </c>
       <c r="F9">
-        <v>6.065217391304348</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="G9">
-        <v>4.375</v>
+        <v>5.1875</v>
       </c>
       <c r="H9">
-        <v>5.964285714285714</v>
+        <v>5.690476190476191</v>
       </c>
       <c r="I9">
-        <v>6.113636363636363</v>
+        <v>6.158536585365853</v>
       </c>
       <c r="J9">
-        <v>6.5</v>
+        <v>6.761904761904762</v>
       </c>
       <c r="K9">
-        <v>4.875</v>
+        <v>5.53125</v>
       </c>
       <c r="L9">
-        <v>6.297619047619047</v>
+        <v>5.958333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -823,34 +823,34 @@
         <v>19</v>
       </c>
       <c r="C10">
-        <v>6.5</v>
+        <v>6.125</v>
       </c>
       <c r="D10">
-        <v>6.25</v>
+        <v>5.535714285714286</v>
       </c>
       <c r="E10">
-        <v>6.25</v>
+        <v>5.725</v>
       </c>
       <c r="F10">
-        <v>6.666666666666667</v>
+        <v>5.869565217391305</v>
       </c>
       <c r="G10">
+        <v>4.1875</v>
+      </c>
+      <c r="H10">
         <v>5.5</v>
       </c>
-      <c r="H10">
-        <v>6.25</v>
-      </c>
       <c r="I10">
-        <v>6.75</v>
+        <v>5.9625</v>
       </c>
       <c r="J10">
-        <v>7.5</v>
+        <v>6.413043478260869</v>
       </c>
       <c r="K10">
-        <v>6.25</v>
+        <v>4.78125</v>
       </c>
       <c r="L10">
-        <v>6.75</v>
+        <v>5.654761904761905</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -861,34 +861,34 @@
         <v>20</v>
       </c>
       <c r="C11">
-        <v>6.3125</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>5.967391304347826</v>
+        <v>5.715909090909091</v>
       </c>
       <c r="E11">
-        <v>6.060975609756097</v>
+        <v>5.939024390243903</v>
       </c>
       <c r="F11">
-        <v>6.065217391304348</v>
+        <v>5.928571428571429</v>
       </c>
       <c r="G11">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="H11">
-        <v>6.010869565217392</v>
+        <v>5.727272727272728</v>
       </c>
       <c r="I11">
-        <v>6.512195121951219</v>
+        <v>6.073170731707317</v>
       </c>
       <c r="J11">
-        <v>6.826086956521739</v>
+        <v>6.571428571428571</v>
       </c>
       <c r="K11">
-        <v>6.09375</v>
+        <v>5.03125</v>
       </c>
       <c r="L11">
-        <v>6.402173913043478</v>
+        <v>6.011363636363637</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -899,34 +899,34 @@
         <v>21</v>
       </c>
       <c r="C12">
-        <v>6.1875</v>
+        <v>6.055555555555555</v>
       </c>
       <c r="D12">
-        <v>5.82051282051282</v>
+        <v>5.772727272727272</v>
       </c>
       <c r="E12">
-        <v>5.987804878048781</v>
+        <v>5.864864864864865</v>
       </c>
       <c r="F12">
-        <v>6.038461538461538</v>
+        <v>6.043478260869565</v>
       </c>
       <c r="G12">
-        <v>5.0625</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="H12">
-        <v>5.705128205128205</v>
+        <v>5.875</v>
       </c>
       <c r="I12">
-        <v>6.26829268292683</v>
+        <v>6.04054054054054</v>
       </c>
       <c r="J12">
-        <v>6.653846153846154</v>
+        <v>6.913043478260869</v>
       </c>
       <c r="K12">
-        <v>5.5625</v>
+        <v>5.305555555555555</v>
       </c>
       <c r="L12">
-        <v>6.044871794871795</v>
+        <v>6.232954545454546</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -937,34 +937,34 @@
         <v>22</v>
       </c>
       <c r="C13">
-        <v>6.1875</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>5.595238095238095</v>
+        <v>5.922222222222222</v>
       </c>
       <c r="E13">
-        <v>5.804347826086956</v>
+        <v>5.8</v>
       </c>
       <c r="F13">
-        <v>5.833333333333333</v>
+        <v>6.022727272727272</v>
       </c>
       <c r="G13">
-        <v>4.0625</v>
+        <v>4.5</v>
       </c>
       <c r="H13">
-        <v>5.630952380952381</v>
+        <v>5.911111111111111</v>
       </c>
       <c r="I13">
-        <v>6.086956521739131</v>
+        <v>5.875</v>
       </c>
       <c r="J13">
-        <v>6.095238095238095</v>
+        <v>6.636363636363637</v>
       </c>
       <c r="K13">
-        <v>4.5625</v>
+        <v>4.875</v>
       </c>
       <c r="L13">
-        <v>5.827380952380953</v>
+        <v>6.233333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -978,31 +978,31 @@
         <v>6.4375</v>
       </c>
       <c r="D14">
-        <v>6.128205128205129</v>
+        <v>5.848837209302325</v>
       </c>
       <c r="E14">
-        <v>6.13953488372093</v>
+        <v>5.930232558139535</v>
       </c>
       <c r="F14">
-        <v>6.37037037037037</v>
+        <v>6.047619047619047</v>
       </c>
       <c r="G14">
-        <v>5.4375</v>
+        <v>6.0625</v>
       </c>
       <c r="H14">
-        <v>6.294871794871795</v>
+        <v>5.755813953488372</v>
       </c>
       <c r="I14">
-        <v>6.348837209302325</v>
+        <v>6.093023255813954</v>
       </c>
       <c r="J14">
-        <v>7.518518518518518</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K14">
-        <v>6.3125</v>
+        <v>6.8125</v>
       </c>
       <c r="L14">
-        <v>6.897435897435898</v>
+        <v>6.069767441860465</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1016,31 +1016,31 @@
         <v>6.125</v>
       </c>
       <c r="D15">
-        <v>5.918604651162791</v>
+        <v>6.021276595744681</v>
       </c>
       <c r="E15">
-        <v>6.113636363636363</v>
+        <v>6.064102564102564</v>
       </c>
       <c r="F15">
-        <v>6.166666666666667</v>
+        <v>6.020833333333333</v>
       </c>
       <c r="G15">
-        <v>5.5</v>
+        <v>5.4375</v>
       </c>
       <c r="H15">
-        <v>5.895348837209302</v>
+        <v>6.127659574468085</v>
       </c>
       <c r="I15">
-        <v>6.443181818181818</v>
+        <v>6.487179487179487</v>
       </c>
       <c r="J15">
-        <v>6.595238095238095</v>
+        <v>6.541666666666667</v>
       </c>
       <c r="K15">
-        <v>5.90625</v>
+        <v>5.8125</v>
       </c>
       <c r="L15">
-        <v>6.197674418604652</v>
+        <v>6.563829787234043</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1051,34 +1051,34 @@
         <v>25</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>6.277777777777778</v>
       </c>
       <c r="D16">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="E16">
-        <v>6.4</v>
+        <v>6.023255813953488</v>
       </c>
       <c r="F16">
-        <v>6.833333333333333</v>
+        <v>6.152173913043478</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>5.277777777777778</v>
       </c>
       <c r="H16">
-        <v>6.8</v>
+        <v>5.6875</v>
       </c>
       <c r="I16">
-        <v>6.9</v>
+        <v>6.255813953488372</v>
       </c>
       <c r="J16">
-        <v>8.5</v>
+        <v>6.869565217391305</v>
       </c>
       <c r="K16">
-        <v>6.25</v>
+        <v>5.888888888888889</v>
       </c>
       <c r="L16">
-        <v>7.4</v>
+        <v>6.025</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1089,34 +1089,34 @@
         <v>26</v>
       </c>
       <c r="C17">
-        <v>6.25</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="D17">
-        <v>5.841463414634147</v>
+        <v>5.773809523809524</v>
       </c>
       <c r="E17">
-        <v>5.723684210526316</v>
+        <v>5.904761904761905</v>
       </c>
       <c r="F17">
-        <v>5.863636363636363</v>
+        <v>6.16</v>
       </c>
       <c r="G17">
-        <v>4.875</v>
+        <v>4.222222222222222</v>
       </c>
       <c r="H17">
-        <v>5.73170731707317</v>
+        <v>5.869047619047619</v>
       </c>
       <c r="I17">
-        <v>5.605263157894737</v>
+        <v>6.190476190476191</v>
       </c>
       <c r="J17">
-        <v>6.227272727272728</v>
+        <v>6.86</v>
       </c>
       <c r="K17">
-        <v>5.5625</v>
+        <v>4.694444444444445</v>
       </c>
       <c r="L17">
-        <v>6.036585365853658</v>
+        <v>6.154761904761905</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1127,34 +1127,34 @@
         <v>27</v>
       </c>
       <c r="C18">
-        <v>6.125</v>
+        <v>6.25</v>
       </c>
       <c r="D18">
-        <v>5.833333333333333</v>
+        <v>6.055555555555555</v>
       </c>
       <c r="E18">
-        <v>6.135135135135135</v>
+        <v>5.954545454545454</v>
       </c>
       <c r="F18">
-        <v>6.211538461538462</v>
+        <v>6.3</v>
       </c>
       <c r="G18">
-        <v>4.8125</v>
+        <v>5.75</v>
       </c>
       <c r="H18">
-        <v>5.84375</v>
+        <v>6.055555555555555</v>
       </c>
       <c r="I18">
-        <v>6.743243243243243</v>
+        <v>6.227272727272728</v>
       </c>
       <c r="J18">
-        <v>6.923076923076923</v>
+        <v>6.8</v>
       </c>
       <c r="K18">
-        <v>5.1875</v>
+        <v>6.25</v>
       </c>
       <c r="L18">
-        <v>6.098958333333333</v>
+        <v>6.388888888888889</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1165,34 +1165,34 @@
         <v>28</v>
       </c>
       <c r="C19">
-        <v>6.1875</v>
+        <v>6.0625</v>
       </c>
       <c r="D19">
-        <v>5.9625</v>
+        <v>6.088888888888889</v>
       </c>
       <c r="E19">
-        <v>6.118421052631579</v>
+        <v>6.094594594594595</v>
       </c>
       <c r="F19">
-        <v>6.113636363636363</v>
+        <v>6.413043478260869</v>
       </c>
       <c r="G19">
-        <v>5.0625</v>
+        <v>4.0625</v>
       </c>
       <c r="H19">
-        <v>6.0875</v>
+        <v>6.4</v>
       </c>
       <c r="I19">
-        <v>6.460526315789473</v>
+        <v>6.283783783783784</v>
       </c>
       <c r="J19">
-        <v>6.454545454545454</v>
+        <v>7.5</v>
       </c>
       <c r="K19">
-        <v>5.5</v>
+        <v>4.59375</v>
       </c>
       <c r="L19">
-        <v>6.4375</v>
+        <v>6.972222222222222</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1203,34 +1203,34 @@
         <v>29</v>
       </c>
       <c r="C20">
-        <v>6.125</v>
+        <v>6.25</v>
       </c>
       <c r="D20">
-        <v>5.797872340425532</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="E20">
-        <v>5.943181818181818</v>
+        <v>5.85</v>
       </c>
       <c r="F20">
-        <v>6.0625</v>
+        <v>5.5</v>
       </c>
       <c r="G20">
-        <v>4.0625</v>
+        <v>4.75</v>
       </c>
       <c r="H20">
-        <v>5.861702127659575</v>
+        <v>5.75</v>
       </c>
       <c r="I20">
-        <v>6.113636363636363</v>
+        <v>6.1</v>
       </c>
       <c r="J20">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="K20">
-        <v>4.53125</v>
+        <v>5.25</v>
       </c>
       <c r="L20">
-        <v>6.196808510638298</v>
+        <v>5.958333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1241,34 +1241,34 @@
         <v>30</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>5.9375</v>
       </c>
       <c r="D21">
-        <v>5.9625</v>
+        <v>6.058139534883721</v>
       </c>
       <c r="E21">
-        <v>6.166666666666667</v>
+        <v>6.177777777777778</v>
       </c>
       <c r="F21">
-        <v>6.282608695652174</v>
+        <v>6.159090909090909</v>
       </c>
       <c r="G21">
-        <v>5.125</v>
+        <v>4.8125</v>
       </c>
       <c r="H21">
-        <v>5.875</v>
+        <v>6.255813953488372</v>
       </c>
       <c r="I21">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J21">
-        <v>7.260869565217392</v>
+        <v>7.159090909090909</v>
       </c>
       <c r="K21">
-        <v>5.375</v>
+        <v>5.03125</v>
       </c>
       <c r="L21">
-        <v>6.18125</v>
+        <v>6.761627906976744</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1279,34 +1279,34 @@
         <v>31</v>
       </c>
       <c r="C22">
-        <v>6.055555555555555</v>
+        <v>6.25</v>
       </c>
       <c r="D22">
-        <v>6.131578947368421</v>
+        <v>5.697674418604652</v>
       </c>
       <c r="E22">
-        <v>6.25531914893617</v>
+        <v>5.977777777777778</v>
       </c>
       <c r="F22">
-        <v>6.222222222222222</v>
+        <v>5.970588235294118</v>
       </c>
       <c r="G22">
-        <v>5.388888888888889</v>
+        <v>4.1875</v>
       </c>
       <c r="H22">
-        <v>6.315789473684211</v>
+        <v>5.755813953488372</v>
       </c>
       <c r="I22">
-        <v>7.117021276595745</v>
+        <v>6.122222222222222</v>
       </c>
       <c r="J22">
-        <v>7.111111111111111</v>
+        <v>6.352941176470588</v>
       </c>
       <c r="K22">
-        <v>5.694444444444445</v>
+        <v>4.875</v>
       </c>
       <c r="L22">
-        <v>6.75</v>
+        <v>6.046511627906977</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1317,34 +1317,34 @@
         <v>32</v>
       </c>
       <c r="C23">
-        <v>6.0625</v>
+        <v>6.055555555555555</v>
       </c>
       <c r="D23">
-        <v>5.855555555555555</v>
+        <v>6.034883720930233</v>
       </c>
       <c r="E23">
-        <v>5.8125</v>
+        <v>6.121621621621622</v>
       </c>
       <c r="F23">
-        <v>5.880952380952381</v>
+        <v>6.28</v>
       </c>
       <c r="G23">
-        <v>4.3125</v>
+        <v>5.5</v>
       </c>
       <c r="H23">
-        <v>5.855555555555555</v>
+        <v>6.046511627906977</v>
       </c>
       <c r="I23">
-        <v>5.975</v>
+        <v>6.324324324324325</v>
       </c>
       <c r="J23">
-        <v>6.214285714285714</v>
+        <v>7.14</v>
       </c>
       <c r="K23">
-        <v>4.71875</v>
+        <v>5.805555555555555</v>
       </c>
       <c r="L23">
-        <v>6.122222222222222</v>
+        <v>6.424418604651163</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1355,34 +1355,34 @@
         <v>33</v>
       </c>
       <c r="C24">
-        <v>6.3125</v>
+        <v>5.9</v>
       </c>
       <c r="D24">
-        <v>5.825581395348837</v>
+        <v>6.1</v>
       </c>
       <c r="E24">
-        <v>5.956521739130435</v>
+        <v>6.174418604651163</v>
       </c>
       <c r="F24">
-        <v>5.95</v>
+        <v>6.305555555555555</v>
       </c>
       <c r="G24">
-        <v>5.8125</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>5.744186046511628</v>
+        <v>6.275</v>
       </c>
       <c r="I24">
-        <v>6.163043478260869</v>
+        <v>6.976744186046512</v>
       </c>
       <c r="J24">
-        <v>6.575</v>
+        <v>7.527777777777778</v>
       </c>
       <c r="K24">
-        <v>6.40625</v>
+        <v>5.2</v>
       </c>
       <c r="L24">
-        <v>6.034883720930233</v>
+        <v>6.66875</v>
       </c>
     </row>
   </sheetData>

--- a/voti_contro.xlsx
+++ b/voti_contro.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>squadra</t>
   </si>
@@ -49,64 +49,73 @@
     <t>MediaConMod_D</t>
   </si>
   <si>
+    <t>INTER</t>
+  </si>
+  <si>
+    <t>SALERNITANA</t>
+  </si>
+  <si>
+    <t>MONZA</t>
+  </si>
+  <si>
+    <t>GENOA</t>
+  </si>
+  <si>
+    <t>VERONA</t>
+  </si>
+  <si>
+    <t>MILAN</t>
+  </si>
+  <si>
+    <t>SASSUOLO</t>
+  </si>
+  <si>
+    <t>PARMA</t>
+  </si>
+  <si>
+    <t>NAPOLI</t>
+  </si>
+  <si>
+    <t>UDINESE</t>
+  </si>
+  <si>
+    <t>ATALANTA</t>
+  </si>
+  <si>
+    <t>FROSINONE</t>
+  </si>
+  <si>
+    <t>LAZIO</t>
+  </si>
+  <si>
     <t>EMPOLI</t>
   </si>
   <si>
     <t>JUVENTUS</t>
   </si>
   <si>
-    <t>VERONA</t>
-  </si>
-  <si>
-    <t>GENOA</t>
+    <t>LECCE</t>
+  </si>
+  <si>
+    <t>FIORENTINA</t>
+  </si>
+  <si>
+    <t>VENEZIA</t>
   </si>
   <si>
     <t>TORINO</t>
   </si>
   <si>
-    <t>FIORENTINA</t>
-  </si>
-  <si>
-    <t>LECCE</t>
+    <t>CAGLIARI</t>
+  </si>
+  <si>
+    <t>BOLOGNA</t>
   </si>
   <si>
     <t>ROMA</t>
   </si>
   <si>
-    <t>BOLOGNA</t>
-  </si>
-  <si>
-    <t>CAGLIARI</t>
-  </si>
-  <si>
-    <t>UDINESE</t>
-  </si>
-  <si>
-    <t>ATALANTA</t>
-  </si>
-  <si>
-    <t>NAPOLI</t>
-  </si>
-  <si>
-    <t>INTER</t>
-  </si>
-  <si>
-    <t>MONZA</t>
-  </si>
-  <si>
-    <t>SALERNITANA</t>
-  </si>
-  <si>
-    <t>MILAN</t>
-  </si>
-  <si>
-    <t>SASSUOLO</t>
-  </si>
-  <si>
-    <t>LAZIO</t>
-  </si>
-  <si>
-    <t>FROSINONE</t>
+    <t>COMO</t>
   </si>
 </sst>
 </file>
@@ -464,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -510,34 +519,34 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>6.125</v>
+        <v>6.0625</v>
       </c>
       <c r="D2">
-        <v>6.184782608695652</v>
+        <v>5.636363636363637</v>
       </c>
       <c r="E2">
-        <v>6.075757575757576</v>
+        <v>5.809523809523809</v>
       </c>
       <c r="F2">
-        <v>6.0625</v>
+        <v>5.8125</v>
       </c>
       <c r="G2">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="H2">
-        <v>6.326086956521739</v>
+        <v>5.659090909090909</v>
       </c>
       <c r="I2">
-        <v>6.348484848484849</v>
+        <v>5.857142857142857</v>
       </c>
       <c r="J2">
-        <v>6.708333333333333</v>
+        <v>5.9375</v>
       </c>
       <c r="K2">
-        <v>5.9375</v>
+        <v>4.15625</v>
       </c>
       <c r="L2">
-        <v>6.831521739130435</v>
+        <v>5.943181818181818</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -548,34 +557,34 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>6.5</v>
+        <v>6.055555555555555</v>
       </c>
       <c r="D3">
-        <v>6.1</v>
+        <v>6.131578947368421</v>
       </c>
       <c r="E3">
-        <v>6.054347826086956</v>
+        <v>6.25531914893617</v>
       </c>
       <c r="F3">
-        <v>5.958333333333333</v>
+        <v>6.222222222222222</v>
       </c>
       <c r="G3">
-        <v>5.4375</v>
+        <v>5.388888888888889</v>
       </c>
       <c r="H3">
-        <v>6.457142857142857</v>
+        <v>6.315789473684211</v>
       </c>
       <c r="I3">
-        <v>6.076086956521739</v>
+        <v>7.117021276595745</v>
       </c>
       <c r="J3">
-        <v>6.125</v>
+        <v>7.111111111111111</v>
       </c>
       <c r="K3">
-        <v>6.3125</v>
+        <v>5.694444444444445</v>
       </c>
       <c r="L3">
-        <v>7.05</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -586,34 +595,34 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>5.8125</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>5.790697674418604</v>
+        <v>5.944444444444445</v>
       </c>
       <c r="E4">
-        <v>6.034090909090909</v>
+        <v>6.089743589743589</v>
       </c>
       <c r="F4">
-        <v>5.921052631578948</v>
+        <v>6.208333333333333</v>
       </c>
       <c r="G4">
-        <v>4.5625</v>
+        <v>5.125</v>
       </c>
       <c r="H4">
-        <v>5.802325581395348</v>
+        <v>5.966666666666667</v>
       </c>
       <c r="I4">
-        <v>6.386363636363637</v>
+        <v>6.269230769230769</v>
       </c>
       <c r="J4">
-        <v>6.631578947368421</v>
+        <v>7.125</v>
       </c>
       <c r="K4">
-        <v>4.9375</v>
+        <v>5.375</v>
       </c>
       <c r="L4">
-        <v>6.081395348837209</v>
+        <v>6.277777777777778</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -624,34 +633,34 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>6.1875</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>5.73170731707317</v>
+        <v>5.766666666666667</v>
       </c>
       <c r="E5">
-        <v>5.964285714285714</v>
+        <v>5.975609756097561</v>
       </c>
       <c r="F5">
-        <v>5.928571428571429</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>4.6875</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>5.75609756097561</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="I5">
-        <v>6.238095238095238</v>
+        <v>6.073170731707317</v>
       </c>
       <c r="J5">
-        <v>6.452380952380953</v>
+        <v>6.825</v>
       </c>
       <c r="K5">
-        <v>5.125</v>
+        <v>5.28125</v>
       </c>
       <c r="L5">
-        <v>6.048780487804878</v>
+        <v>6.155555555555556</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -662,34 +671,34 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>6.1875</v>
+        <v>5.875</v>
       </c>
       <c r="D6">
-        <v>5.878048780487805</v>
+        <v>5.744186046511628</v>
       </c>
       <c r="E6">
-        <v>5.963414634146342</v>
+        <v>5.797297297297297</v>
       </c>
       <c r="F6">
-        <v>6.041666666666667</v>
+        <v>5.913043478260869</v>
       </c>
       <c r="G6">
-        <v>5.1875</v>
+        <v>4.5</v>
       </c>
       <c r="H6">
-        <v>5.804878048780488</v>
+        <v>5.813953488372093</v>
       </c>
       <c r="I6">
-        <v>6.195121951219512</v>
+        <v>5.945945945945946</v>
       </c>
       <c r="J6">
-        <v>6.5</v>
+        <v>6.521739130434782</v>
       </c>
       <c r="K6">
-        <v>5.6875</v>
+        <v>4.90625</v>
       </c>
       <c r="L6">
-        <v>6.140243902439025</v>
+        <v>6.156976744186046</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -700,34 +709,34 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>6.3125</v>
+        <v>6.125</v>
       </c>
       <c r="D7">
-        <v>5.837209302325581</v>
+        <v>6.079545454545454</v>
       </c>
       <c r="E7">
-        <v>5.953488372093023</v>
+        <v>6.1</v>
       </c>
       <c r="F7">
-        <v>6.113636363636363</v>
+        <v>6.42</v>
       </c>
       <c r="G7">
-        <v>4.5625</v>
+        <v>4.25</v>
       </c>
       <c r="H7">
-        <v>5.918604651162791</v>
+        <v>6.352272727272728</v>
       </c>
       <c r="I7">
-        <v>6.197674418604652</v>
+        <v>6.257142857142857</v>
       </c>
       <c r="J7">
-        <v>6.704545454545454</v>
+        <v>7.42</v>
       </c>
       <c r="K7">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="L7">
-        <v>6.215116279069767</v>
+        <v>6.926136363636363</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -738,34 +747,34 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>6.375</v>
+        <v>5.9375</v>
       </c>
       <c r="D8">
-        <v>5.888888888888889</v>
+        <v>6.097560975609756</v>
       </c>
       <c r="E8">
-        <v>5.920454545454546</v>
+        <v>6.174418604651163</v>
       </c>
       <c r="F8">
-        <v>5.954545454545454</v>
+        <v>6.227272727272728</v>
       </c>
       <c r="G8">
-        <v>5.5625</v>
+        <v>4.8125</v>
       </c>
       <c r="H8">
-        <v>5.9</v>
+        <v>6.292682926829269</v>
       </c>
       <c r="I8">
-        <v>6.193181818181818</v>
+        <v>6.709302325581396</v>
       </c>
       <c r="J8">
-        <v>6.477272727272728</v>
+        <v>7.340909090909091</v>
       </c>
       <c r="K8">
-        <v>6.21875</v>
+        <v>5.03125</v>
       </c>
       <c r="L8">
-        <v>6.233333333333333</v>
+        <v>6.829268292682927</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -776,34 +785,34 @@
         <v>18</v>
       </c>
       <c r="C9">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="D9">
+        <v>5.777777777777778</v>
+      </c>
+      <c r="E9">
+        <v>5.964285714285714</v>
+      </c>
+      <c r="F9">
+        <v>5.6875</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>5.888888888888889</v>
+      </c>
+      <c r="I9">
+        <v>6.357142857142857</v>
+      </c>
+      <c r="J9">
         <v>6.1875</v>
       </c>
-      <c r="D9">
-        <v>5.9875</v>
-      </c>
-      <c r="E9">
-        <v>6.135135135135135</v>
-      </c>
-      <c r="F9">
-        <v>6.104166666666667</v>
-      </c>
-      <c r="G9">
-        <v>5.0625</v>
-      </c>
-      <c r="H9">
-        <v>6.1125</v>
-      </c>
-      <c r="I9">
-        <v>6.486486486486487</v>
-      </c>
-      <c r="J9">
-        <v>6.395833333333333</v>
-      </c>
       <c r="K9">
-        <v>5.5</v>
+        <v>5.583333333333333</v>
       </c>
       <c r="L9">
-        <v>6.4875</v>
+        <v>6.125</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -814,34 +823,34 @@
         <v>19</v>
       </c>
       <c r="C10">
-        <v>6.0625</v>
+        <v>6.3125</v>
       </c>
       <c r="D10">
-        <v>5.738095238095238</v>
+        <v>6.1125</v>
       </c>
       <c r="E10">
-        <v>5.707317073170731</v>
+        <v>6.1375</v>
       </c>
       <c r="F10">
-        <v>5.975</v>
+        <v>6.216666666666667</v>
       </c>
       <c r="G10">
-        <v>4.5</v>
+        <v>5.5625</v>
       </c>
       <c r="H10">
-        <v>5.571428571428571</v>
+        <v>6.1875</v>
       </c>
       <c r="I10">
-        <v>5.573170731707317</v>
+        <v>6.275</v>
       </c>
       <c r="J10">
-        <v>6.5</v>
+        <v>7.133333333333334</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6.28125</v>
       </c>
       <c r="L10">
-        <v>5.779761904761905</v>
+        <v>6.7625</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -852,34 +861,34 @@
         <v>20</v>
       </c>
       <c r="C11">
+        <v>6.0625</v>
+      </c>
+      <c r="D11">
+        <v>5.837209302325581</v>
+      </c>
+      <c r="E11">
+        <v>5.943181818181818</v>
+      </c>
+      <c r="F11">
+        <v>6.095238095238095</v>
+      </c>
+      <c r="G11">
+        <v>5.1875</v>
+      </c>
+      <c r="H11">
+        <v>5.755813953488372</v>
+      </c>
+      <c r="I11">
         <v>6.125</v>
       </c>
-      <c r="D11">
-        <v>5.840425531914893</v>
-      </c>
-      <c r="E11">
-        <v>6.089743589743589</v>
-      </c>
-      <c r="F11">
-        <v>6.28</v>
-      </c>
-      <c r="G11">
-        <v>4.6875</v>
-      </c>
-      <c r="H11">
-        <v>5.840425531914893</v>
-      </c>
-      <c r="I11">
-        <v>6.653846153846154</v>
-      </c>
       <c r="J11">
-        <v>7.18</v>
+        <v>6.547619047619047</v>
       </c>
       <c r="K11">
-        <v>5.0625</v>
+        <v>5.53125</v>
       </c>
       <c r="L11">
-        <v>6.101063829787234</v>
+        <v>6.023255813953488</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -890,34 +899,34 @@
         <v>21</v>
       </c>
       <c r="C12">
-        <v>6.0625</v>
+        <v>6.3125</v>
       </c>
       <c r="D12">
-        <v>5.895348837209302</v>
+        <v>5.647727272727272</v>
       </c>
       <c r="E12">
-        <v>6.071428571428571</v>
+        <v>5.845238095238095</v>
       </c>
       <c r="F12">
-        <v>6.181818181818182</v>
+        <v>5.925</v>
       </c>
       <c r="G12">
-        <v>5.0625</v>
+        <v>4.75</v>
       </c>
       <c r="H12">
-        <v>5.86046511627907</v>
+        <v>5.613636363636363</v>
       </c>
       <c r="I12">
-        <v>6.369047619047619</v>
+        <v>6.214285714285714</v>
       </c>
       <c r="J12">
-        <v>6.727272727272728</v>
+        <v>6.4</v>
       </c>
       <c r="K12">
-        <v>5.40625</v>
+        <v>5.4375</v>
       </c>
       <c r="L12">
-        <v>6.133720930232558</v>
+        <v>5.823863636363637</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -928,34 +937,34 @@
         <v>22</v>
       </c>
       <c r="C13">
-        <v>6.1875</v>
+        <v>6.3125</v>
       </c>
       <c r="D13">
-        <v>5.634146341463414</v>
+        <v>5.825581395348837</v>
       </c>
       <c r="E13">
-        <v>5.797872340425532</v>
+        <v>5.956521739130435</v>
       </c>
       <c r="F13">
-        <v>5.863636363636363</v>
+        <v>5.95</v>
       </c>
       <c r="G13">
-        <v>4.1875</v>
+        <v>5.8125</v>
       </c>
       <c r="H13">
-        <v>5.658536585365853</v>
+        <v>5.744186046511628</v>
       </c>
       <c r="I13">
-        <v>6.074468085106383</v>
+        <v>6.163043478260869</v>
       </c>
       <c r="J13">
-        <v>6.090909090909091</v>
+        <v>6.575</v>
       </c>
       <c r="K13">
-        <v>4.6875</v>
+        <v>6.40625</v>
       </c>
       <c r="L13">
-        <v>5.853658536585366</v>
+        <v>6.034883720930233</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -966,34 +975,34 @@
         <v>23</v>
       </c>
       <c r="C14">
-        <v>6.5</v>
+        <v>6.125</v>
       </c>
       <c r="D14">
-        <v>6.130952380952381</v>
+        <v>5.875</v>
       </c>
       <c r="E14">
-        <v>6.158536585365853</v>
+        <v>5.785714285714286</v>
       </c>
       <c r="F14">
-        <v>6.384615384615385</v>
+        <v>6.108695652173913</v>
       </c>
       <c r="G14">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="H14">
-        <v>6.321428571428571</v>
+        <v>5.852272727272728</v>
       </c>
       <c r="I14">
-        <v>6.512195121951219</v>
+        <v>5.880952380952381</v>
       </c>
       <c r="J14">
-        <v>7.346153846153846</v>
+        <v>6.869565217391305</v>
       </c>
       <c r="K14">
-        <v>6.46875</v>
+        <v>4.96875</v>
       </c>
       <c r="L14">
-        <v>6.898809523809524</v>
+        <v>6.153409090909091</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1004,34 +1013,34 @@
         <v>24</v>
       </c>
       <c r="C15">
-        <v>6.1875</v>
+        <v>6.3125</v>
       </c>
       <c r="D15">
-        <v>5.782608695652174</v>
+        <v>6.071428571428571</v>
       </c>
       <c r="E15">
-        <v>5.837209302325581</v>
+        <v>5.894736842105263</v>
       </c>
       <c r="F15">
-        <v>6.058823529411764</v>
+        <v>5.76</v>
       </c>
       <c r="G15">
-        <v>4.1875</v>
+        <v>5.6875</v>
       </c>
       <c r="H15">
-        <v>5.771739130434782</v>
+        <v>6.083333333333333</v>
       </c>
       <c r="I15">
-        <v>6.011627906976744</v>
+        <v>6.223684210526316</v>
       </c>
       <c r="J15">
-        <v>6.441176470588236</v>
+        <v>6.02</v>
       </c>
       <c r="K15">
-        <v>4.71875</v>
+        <v>6.28125</v>
       </c>
       <c r="L15">
-        <v>6.076086956521739</v>
+        <v>6.476190476190476</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1042,34 +1051,34 @@
         <v>25</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>6.4375</v>
       </c>
       <c r="D16">
-        <v>5.95</v>
+        <v>5.942857142857143</v>
       </c>
       <c r="E16">
-        <v>6.141025641025641</v>
+        <v>5.92</v>
       </c>
       <c r="F16">
-        <v>6.282608695652174</v>
+        <v>5.909090909090909</v>
       </c>
       <c r="G16">
-        <v>5.125</v>
+        <v>4.75</v>
       </c>
       <c r="H16">
-        <v>5.8625</v>
+        <v>6.185714285714286</v>
       </c>
       <c r="I16">
-        <v>6.487179487179487</v>
+        <v>5.9</v>
       </c>
       <c r="J16">
-        <v>7.391304347826087</v>
+        <v>6.136363636363637</v>
       </c>
       <c r="K16">
-        <v>5.375</v>
+        <v>5.5625</v>
       </c>
       <c r="L16">
-        <v>6.1625</v>
+        <v>6.764285714285714</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1080,34 +1089,34 @@
         <v>26</v>
       </c>
       <c r="C17">
-        <v>6.055555555555555</v>
+        <v>6.125</v>
       </c>
       <c r="D17">
-        <v>6.131578947368421</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>6.25531914893617</v>
+        <v>6.05</v>
       </c>
       <c r="F17">
-        <v>6.222222222222222</v>
+        <v>5.931818181818182</v>
       </c>
       <c r="G17">
-        <v>5.388888888888889</v>
+        <v>5.3125</v>
       </c>
       <c r="H17">
-        <v>6.315789473684211</v>
+        <v>6.091836734693878</v>
       </c>
       <c r="I17">
-        <v>7.117021276595745</v>
+        <v>6.45</v>
       </c>
       <c r="J17">
-        <v>7.111111111111111</v>
+        <v>6.477272727272728</v>
       </c>
       <c r="K17">
-        <v>5.694444444444445</v>
+        <v>5.6875</v>
       </c>
       <c r="L17">
-        <v>6.75</v>
+        <v>6.510204081632653</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1118,34 +1127,34 @@
         <v>27</v>
       </c>
       <c r="C18">
-        <v>6.3125</v>
+        <v>6.25</v>
       </c>
       <c r="D18">
-        <v>5.895348837209302</v>
+        <v>5.886363636363637</v>
       </c>
       <c r="E18">
-        <v>6.088235294117647</v>
+        <v>5.848837209302325</v>
       </c>
       <c r="F18">
-        <v>6.134615384615385</v>
+        <v>6.041666666666667</v>
       </c>
       <c r="G18">
-        <v>4.0625</v>
+        <v>4.375</v>
       </c>
       <c r="H18">
-        <v>6.058139534883721</v>
+        <v>5.954545454545454</v>
       </c>
       <c r="I18">
-        <v>6.338235294117647</v>
+        <v>6.034883720930233</v>
       </c>
       <c r="J18">
-        <v>6.980769230769231</v>
+        <v>6.583333333333333</v>
       </c>
       <c r="K18">
-        <v>4.6875</v>
+        <v>5.03125</v>
       </c>
       <c r="L18">
-        <v>6.453488372093023</v>
+        <v>6.267045454545454</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1156,34 +1165,34 @@
         <v>28</v>
       </c>
       <c r="C19">
-        <v>5.9375</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="D19">
-        <v>6.097560975609756</v>
+        <v>6.0625</v>
       </c>
       <c r="E19">
-        <v>6.174418604651163</v>
+        <v>6</v>
       </c>
       <c r="F19">
-        <v>6.227272727272728</v>
+        <v>6.125</v>
       </c>
       <c r="G19">
-        <v>4.8125</v>
+        <v>6</v>
       </c>
       <c r="H19">
-        <v>6.292682926829269</v>
+        <v>6.21875</v>
       </c>
       <c r="I19">
-        <v>6.709302325581396</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="J19">
-        <v>7.340909090909091</v>
+        <v>6.4375</v>
       </c>
       <c r="K19">
-        <v>5.03125</v>
+        <v>6.583333333333333</v>
       </c>
       <c r="L19">
-        <v>6.829268292682927</v>
+        <v>6.625</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1194,34 +1203,34 @@
         <v>29</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>6.3125</v>
       </c>
       <c r="D20">
-        <v>5.920454545454546</v>
+        <v>5.769230769230769</v>
       </c>
       <c r="E20">
-        <v>5.75</v>
+        <v>5.988888888888889</v>
       </c>
       <c r="F20">
-        <v>5.909090909090909</v>
+        <v>5.977272727272728</v>
       </c>
       <c r="G20">
-        <v>4.5</v>
+        <v>5.0625</v>
       </c>
       <c r="H20">
-        <v>5.988636363636363</v>
+        <v>5.653846153846154</v>
       </c>
       <c r="I20">
-        <v>5.785714285714286</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="J20">
-        <v>6.227272727272728</v>
+        <v>6.454545454545454</v>
       </c>
       <c r="K20">
-        <v>4.84375</v>
+        <v>5.71875</v>
       </c>
       <c r="L20">
-        <v>6.289772727272728</v>
+        <v>5.987179487179487</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1232,34 +1241,148 @@
         <v>30</v>
       </c>
       <c r="C21">
-        <v>6.3125</v>
+        <v>6.1875</v>
       </c>
       <c r="D21">
-        <v>5.825581395348837</v>
+        <v>5.922222222222222</v>
       </c>
       <c r="E21">
-        <v>5.956521739130435</v>
+        <v>6.1625</v>
       </c>
       <c r="F21">
-        <v>5.95</v>
+        <v>6.134615384615385</v>
       </c>
       <c r="G21">
-        <v>5.8125</v>
+        <v>5.1875</v>
       </c>
       <c r="H21">
-        <v>5.744186046511628</v>
+        <v>5.966666666666667</v>
       </c>
       <c r="I21">
-        <v>6.163043478260869</v>
+        <v>6.65</v>
       </c>
       <c r="J21">
-        <v>6.575</v>
+        <v>6.769230769230769</v>
       </c>
       <c r="K21">
-        <v>6.40625</v>
+        <v>5.6875</v>
       </c>
       <c r="L21">
-        <v>6.034883720930233</v>
+        <v>6.316666666666666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>6.125</v>
+      </c>
+      <c r="D22">
+        <v>5.926829268292683</v>
+      </c>
+      <c r="E22">
+        <v>5.82051282051282</v>
+      </c>
+      <c r="F22">
+        <v>5.94</v>
+      </c>
+      <c r="G22">
+        <v>4.5625</v>
+      </c>
+      <c r="H22">
+        <v>5.914634146341464</v>
+      </c>
+      <c r="I22">
+        <v>5.82051282051282</v>
+      </c>
+      <c r="J22">
+        <v>6.54</v>
+      </c>
+      <c r="K22">
+        <v>5.0625</v>
+      </c>
+      <c r="L22">
+        <v>6.310975609756097</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>6.25</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>6.064102564102564</v>
+      </c>
+      <c r="F23">
+        <v>6.159090909090909</v>
+      </c>
+      <c r="G23">
+        <v>5.25</v>
+      </c>
+      <c r="H23">
+        <v>6.085365853658536</v>
+      </c>
+      <c r="I23">
+        <v>6.294871794871795</v>
+      </c>
+      <c r="J23">
+        <v>6.545454545454546</v>
+      </c>
+      <c r="K23">
+        <v>5.75</v>
+      </c>
+      <c r="L23">
+        <v>6.457317073170731</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="D24">
+        <v>6.25</v>
+      </c>
+      <c r="E24">
+        <v>6.038461538461538</v>
+      </c>
+      <c r="F24">
+        <v>6.318181818181818</v>
+      </c>
+      <c r="G24">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="H24">
+        <v>6.46875</v>
+      </c>
+      <c r="I24">
+        <v>6.153846153846154</v>
+      </c>
+      <c r="J24">
+        <v>7.272727272727272</v>
+      </c>
+      <c r="K24">
+        <v>6.25</v>
+      </c>
+      <c r="L24">
+        <v>7.015625</v>
       </c>
     </row>
   </sheetData>
